--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dumitrasadrian/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BACC3FB-8D8B-AB40-A674-0254A20D2FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1312497E-BDDF-9E47-9A55-240E593AE8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="400" windowWidth="20480" windowHeight="12860" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="428">
   <si>
     <t>Ticker</t>
   </si>
@@ -1451,6 +1451,9 @@
   </si>
   <si>
     <t>Price per exabyte growth rate</t>
+  </si>
+  <si>
+    <t>23.04.2026</t>
   </si>
 </sst>
 </file>
@@ -1458,15 +1461,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="167" formatCode="0.00_);\(0.00\)"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="168" formatCode="0.00_);\(0.00\)"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -2058,7 +2061,7 @@
   <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2096,10 +2099,10 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2110,9 +2113,9 @@
     <xf numFmtId="38" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="7" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2127,7 +2130,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2135,10 +2138,10 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2147,15 +2150,15 @@
     </xf>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="7" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2187,16 +2190,16 @@
     <xf numFmtId="37" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="18" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="20" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="20" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="21" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="21" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2214,14 +2217,14 @@
     <xf numFmtId="37" fontId="19" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="18" fillId="12" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="18" fillId="12" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2242,11 +2245,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2254,9 +2257,9 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2267,7 +2270,7 @@
     <xf numFmtId="37" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2277,21 +2280,21 @@
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="7" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2300,13 +2303,13 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="18" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2335,9 +2338,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="10" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -2373,25 +2376,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="170" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2403,12 +2393,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2416,6 +2400,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2430,12 +2435,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -2475,7 +2478,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2969,7 +2972,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3264,7 +3267,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3613,7 +3616,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4047,7 +4050,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4538,7 +4541,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4962,7 +4965,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5324,7 +5327,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5775,7 +5778,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6226,7 +6229,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12802,12 +12805,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
-    <v>66.510000000000005</v>
+    <v>68.665000000000006</v>
     <v>2.1682999999999999</v>
-    <v>-38.5</v>
-    <v>-6.8959000000000006E-2</v>
-    <v>-7.0372000000000003</v>
-    <v>-1.3538E-2</v>
+    <v>-34.409999999999997</v>
+    <v>-6.9107000000000002E-2</v>
+    <v>1.59</v>
+    <v>3.4300000000000003E-3</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12815,26 +12818,26 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>552</v>
+    <v>467.26</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46227.99995319375</v>
+    <v>46231.985171839842</v>
     <v>4</v>
-    <v>509.56</v>
-    <v>179165755579</v>
+    <v>422.11</v>
+    <v>159763600171</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>538.5</v>
-    <v>36.383299999999998</v>
-    <v>558.29999999999995</v>
-    <v>519.79999999999995</v>
-    <v>512.76279999999997</v>
+    <v>466.09</v>
+    <v>32.448399999999999</v>
+    <v>497.92</v>
+    <v>463.51</v>
+    <v>465.1</v>
     <v>344682100</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>4775567</v>
-    <v>9573210</v>
+    <v>10484193</v>
+    <v>8802793</v>
     <v>2000</v>
   </rv>
   <rv s="4">
@@ -12858,17 +12861,17 @@
     <v>Powered by Refinitiv</v>
     <v>47.14</v>
     <v>39.47</v>
-    <v>-0.24</v>
-    <v>-5.1029999999999999E-3</v>
+    <v>-0.37</v>
+    <v>-7.9719999999999999E-3</v>
     <v>US</v>
-    <v>46.91</v>
+    <v>46.35</v>
     <v>Index</v>
     <v>7</v>
-    <v>46.51</v>
+    <v>45.88</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.83</v>
-    <v>47.03</v>
-    <v>46.79</v>
+    <v>46.3</v>
+    <v>46.41</v>
+    <v>46.04</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13110,9 +13113,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13247,7 +13250,7 @@
       <x:numFmt numFmtId="0" formatCode="General"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
+      <x:numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="14" formatCode="0.00%"/>
@@ -13705,18 +13708,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="246" t="s">
+      <c r="B2" s="243" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="247"/>
-      <c r="E2" s="246" t="s">
+      <c r="C2" s="244"/>
+      <c r="E2" s="243" t="s">
         <v>291</v>
       </c>
-      <c r="F2" s="247"/>
-      <c r="H2" s="246" t="s">
+      <c r="F2" s="244"/>
+      <c r="H2" s="243" t="s">
         <v>332</v>
       </c>
-      <c r="I2" s="247"/>
+      <c r="I2" s="244"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="185" t="s">
@@ -13731,7 +13734,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>181410.19999999998</v>
+        <v>161764.99</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13755,7 +13758,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>180941.19999999998</v>
+        <v>161295.99</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13772,7 +13775,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>519.79999999999995</v>
+        <v>463.51</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13796,14 +13799,14 @@
       </c>
       <c r="C6" s="208" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>512.76279999999997</v>
+        <v>465.1</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>31.18176364727054</v>
+        <v>27.805038992201556</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13820,14 +13823,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-38.5</v>
+        <v>-34.409999999999997</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>16.617534176785259</v>
+        <v>14.817993971299991</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13844,14 +13847,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-7.0372000000000003</v>
+        <v>1.59</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>2.4215837918705786E-2</v>
+        <v>2.7156679575722781E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13859,7 +13862,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.82147990745621413</v>
+        <v>-0.79979990916213262</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13868,14 +13871,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.8959000000000006E-2</v>
+        <v>-6.9107000000000002E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>3.2070026933435941E-2</v>
+        <v>3.5964704105628791E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13884,14 +13887,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.3538E-2</v>
+        <v>3.4300000000000003E-3</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>2.0891879287934196E-2</v>
+        <v>2.3429049759159878E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>372</v>
@@ -13914,7 +13917,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>8.6571758368603321E-4</v>
+        <v>9.7085284028392059E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13923,7 +13926,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>66.510000000000005</v>
+        <v>68.665000000000006</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>101</v>
@@ -13955,7 +13958,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>9573210</v>
+        <v>8802793</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>104</v>
@@ -13971,7 +13974,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>2.5853011572667911E-3</v>
+        <v>2.8992676351044812E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13984,10 +13987,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="248" t="s">
+      <c r="B17" s="245" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="248"/>
+      <c r="C17" s="245"/>
       <c r="E17" s="184" t="s">
         <v>300</v>
       </c>
@@ -14060,14 +14063,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="248" t="s">
+      <c r="B25" s="245" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="248"/>
-      <c r="E25" s="246" t="s">
+      <c r="C25" s="245"/>
+      <c r="E25" s="243" t="s">
         <v>345</v>
       </c>
-      <c r="F25" s="247"/>
+      <c r="F25" s="244"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="184" t="s">
@@ -14081,7 +14084,7 @@
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.79</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14096,7 +14099,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.6789999999999998E-2</v>
+        <v>4.6039999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14116,15 +14119,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="243" t="s">
+      <c r="B33" s="242" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
+      <c r="C33" s="242"/>
+      <c r="D33" s="242"/>
+      <c r="E33" s="242"/>
+      <c r="F33" s="242"/>
+      <c r="G33" s="242"/>
+      <c r="H33" s="242"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14191,31 +14194,31 @@
       </c>
     </row>
     <row r="46" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="243"/>
-      <c r="C46" s="243"/>
-      <c r="D46" s="243"/>
-      <c r="E46" s="243"/>
-      <c r="F46" s="243"/>
-      <c r="G46" s="243"/>
-      <c r="H46" s="243"/>
+      <c r="B46" s="242"/>
+      <c r="C46" s="242"/>
+      <c r="D46" s="242"/>
+      <c r="E46" s="242"/>
+      <c r="F46" s="242"/>
+      <c r="G46" s="242"/>
+      <c r="H46" s="242"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="243" t="s">
+      <c r="B49" s="242" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="243"/>
-      <c r="D49" s="243"/>
-      <c r="E49" s="243"/>
-      <c r="F49" s="243"/>
-      <c r="G49" s="243"/>
-      <c r="H49" s="243"/>
+      <c r="C49" s="242"/>
+      <c r="D49" s="242"/>
+      <c r="E49" s="242"/>
+      <c r="F49" s="242"/>
+      <c r="G49" s="242"/>
+      <c r="H49" s="242"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="41" t="s">
         <v>344</v>
       </c>
       <c r="C51" s="41" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="D51" s="41"/>
       <c r="E51" s="41" t="s">
@@ -14267,24 +14270,24 @@
       </c>
     </row>
     <row r="61" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="243"/>
-      <c r="C61" s="243"/>
-      <c r="D61" s="243"/>
-      <c r="E61" s="243"/>
-      <c r="F61" s="243"/>
-      <c r="G61" s="243"/>
-      <c r="H61" s="243"/>
+      <c r="B61" s="242"/>
+      <c r="C61" s="242"/>
+      <c r="D61" s="242"/>
+      <c r="E61" s="242"/>
+      <c r="F61" s="242"/>
+      <c r="G61" s="242"/>
+      <c r="H61" s="242"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B64" s="243" t="s">
+      <c r="B64" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="243"/>
-      <c r="D64" s="243"/>
-      <c r="E64" s="243"/>
-      <c r="F64" s="243"/>
-      <c r="G64" s="243"/>
-      <c r="H64" s="243"/>
+      <c r="C64" s="242"/>
+      <c r="D64" s="242"/>
+      <c r="E64" s="242"/>
+      <c r="F64" s="242"/>
+      <c r="G64" s="242"/>
+      <c r="H64" s="242"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" s="41" t="s">
@@ -14299,28 +14302,28 @@
       </c>
     </row>
     <row r="71" spans="2:8" ht="5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="243"/>
-      <c r="C71" s="243"/>
-      <c r="D71" s="243"/>
-      <c r="E71" s="243"/>
-      <c r="F71" s="243"/>
-      <c r="G71" s="243"/>
-      <c r="H71" s="243"/>
+      <c r="B71" s="242"/>
+      <c r="C71" s="242"/>
+      <c r="D71" s="242"/>
+      <c r="E71" s="242"/>
+      <c r="F71" s="242"/>
+      <c r="G71" s="242"/>
+      <c r="H71" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B64:H64"/>
     <mergeCell ref="B71:H71"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14390,36 +14393,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="243" t="s">
+      <c r="S2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243"/>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
-      <c r="AA2" s="243" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="243"/>
-      <c r="AC2" s="243"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -14430,32 +14433,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="241" t="s">
+      <c r="S4" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
-      <c r="AA4" s="242"/>
-      <c r="AB4" s="242"/>
-      <c r="AC4" s="242"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -14945,33 +14948,33 @@
       <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="O11" s="5"/>
       <c r="Q11" s="91"/>
-      <c r="S11" s="241" t="s">
+      <c r="S11" s="252" t="s">
         <v>121</v>
       </c>
-      <c r="T11" s="242"/>
-      <c r="U11" s="242"/>
-      <c r="V11" s="242"/>
-      <c r="W11" s="242"/>
-      <c r="X11" s="242"/>
-      <c r="Y11" s="242"/>
-      <c r="Z11" s="242"/>
-      <c r="AA11" s="242"/>
-      <c r="AB11" s="242"/>
-      <c r="AC11" s="242"/>
+      <c r="T11" s="253"/>
+      <c r="U11" s="253"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="253"/>
+      <c r="X11" s="253"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
+      <c r="AA11" s="253"/>
+      <c r="AB11" s="253"/>
+      <c r="AC11" s="253"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B12" s="16" t="s">
@@ -15402,32 +15405,32 @@
     <row r="19" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="86"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="240" t="s">
+      <c r="C19" s="251" t="s">
         <v>424</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="E19" s="240"/>
-      <c r="F19" s="240"/>
-      <c r="G19" s="240"/>
-      <c r="H19" s="240"/>
-      <c r="I19" s="240"/>
-      <c r="J19" s="240"/>
-      <c r="K19" s="240"/>
-      <c r="L19" s="240"/>
+      <c r="D19" s="251"/>
+      <c r="E19" s="251"/>
+      <c r="F19" s="251"/>
+      <c r="G19" s="251"/>
+      <c r="H19" s="251"/>
+      <c r="I19" s="251"/>
+      <c r="J19" s="251"/>
+      <c r="K19" s="251"/>
+      <c r="L19" s="251"/>
       <c r="O19" s="5"/>
-      <c r="S19" s="241" t="s">
+      <c r="S19" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="T19" s="242"/>
-      <c r="U19" s="242"/>
-      <c r="V19" s="242"/>
-      <c r="W19" s="242"/>
-      <c r="X19" s="242"/>
-      <c r="Y19" s="242"/>
-      <c r="Z19" s="242"/>
-      <c r="AA19" s="242"/>
-      <c r="AB19" s="242"/>
-      <c r="AC19" s="242"/>
+      <c r="T19" s="253"/>
+      <c r="U19" s="253"/>
+      <c r="V19" s="253"/>
+      <c r="W19" s="253"/>
+      <c r="X19" s="253"/>
+      <c r="Y19" s="253"/>
+      <c r="Z19" s="253"/>
+      <c r="AA19" s="253"/>
+      <c r="AB19" s="253"/>
+      <c r="AC19" s="253"/>
       <c r="AE19" s="87"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
@@ -15548,23 +15551,23 @@
         <f>Statement!Q208</f>
         <v>610</v>
       </c>
-      <c r="H21" s="258">
+      <c r="H21" s="240">
         <f>G21*(1+H23)</f>
         <v>762.5</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="240">
         <f t="shared" ref="I21:L21" si="22">H21*(1+I23)</f>
         <v>991.25</v>
       </c>
-      <c r="J21" s="258">
+      <c r="J21" s="240">
         <f t="shared" si="22"/>
         <v>1090.375</v>
       </c>
-      <c r="K21" s="258">
+      <c r="K21" s="240">
         <f t="shared" si="22"/>
         <v>1090.375</v>
       </c>
-      <c r="L21" s="258">
+      <c r="L21" s="240">
         <f t="shared" si="22"/>
         <v>981.33749999999998</v>
       </c>
@@ -15647,23 +15650,23 @@
         <f>Statement!Q211</f>
         <v>13.673770491803278</v>
       </c>
-      <c r="H22" s="259">
+      <c r="H22" s="241">
         <f>G22*(1+H24)</f>
         <v>14.494196721311475</v>
       </c>
-      <c r="I22" s="259">
+      <c r="I22" s="241">
         <f t="shared" ref="I22:L22" si="23">H22*(1+I24)</f>
         <v>15.21890655737705</v>
       </c>
-      <c r="J22" s="259">
+      <c r="J22" s="241">
         <f t="shared" si="23"/>
         <v>14.457961229508197</v>
       </c>
-      <c r="K22" s="259">
+      <c r="K22" s="241">
         <f t="shared" si="23"/>
         <v>13.735063168032786</v>
       </c>
-      <c r="L22" s="259">
+      <c r="L22" s="241">
         <f t="shared" si="23"/>
         <v>13.048310009631146</v>
       </c>
@@ -15922,35 +15925,35 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="P2" s="243" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="243"/>
-      <c r="R2" s="243"/>
-      <c r="S2" s="243"/>
-      <c r="T2" s="243"/>
-      <c r="U2" s="243"/>
-      <c r="V2" s="243"/>
-      <c r="W2" s="243"/>
-      <c r="X2" s="243" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="243"/>
-      <c r="Z2" s="243"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -15959,31 +15962,31 @@
     <row r="4" spans="1:30" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="P4" s="242" t="s">
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="P4" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
+      <c r="Q4" s="253"/>
+      <c r="R4" s="253"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
@@ -16178,32 +16181,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="C9" s="240" t="s">
+      <c r="C9" s="251" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="242" t="s">
+      <c r="P9" s="253" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="242"/>
-      <c r="R9" s="242"/>
-      <c r="S9" s="242"/>
-      <c r="T9" s="242"/>
-      <c r="U9" s="242"/>
-      <c r="V9" s="242"/>
-      <c r="W9" s="242"/>
-      <c r="X9" s="242"/>
-      <c r="Y9" s="242"/>
-      <c r="Z9" s="242"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
+      <c r="T9" s="253"/>
+      <c r="U9" s="253"/>
+      <c r="V9" s="253"/>
+      <c r="W9" s="253"/>
+      <c r="X9" s="253"/>
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
       <c r="AB9" s="87">
         <f>AB4</f>
         <v>0</v>
@@ -16680,121 +16683,121 @@
       </c>
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C17" s="240" t="s">
+      <c r="C17" s="251" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="E17" s="240"/>
-      <c r="F17" s="240"/>
-      <c r="G17" s="240"/>
-      <c r="H17" s="240"/>
-      <c r="I17" s="240"/>
-      <c r="J17" s="240"/>
-      <c r="K17" s="240"/>
-      <c r="L17" s="240"/>
-      <c r="P17" s="242" t="s">
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
+      <c r="P17" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="Q17" s="242"/>
-      <c r="R17" s="242"/>
-      <c r="S17" s="242"/>
-      <c r="T17" s="242"/>
-      <c r="U17" s="242"/>
-      <c r="V17" s="242"/>
-      <c r="W17" s="242"/>
-      <c r="X17" s="242"/>
-      <c r="Y17" s="242"/>
-      <c r="Z17" s="242"/>
+      <c r="Q17" s="253"/>
+      <c r="R17" s="253"/>
+      <c r="S17" s="253"/>
+      <c r="T17" s="253"/>
+      <c r="U17" s="253"/>
+      <c r="V17" s="253"/>
+      <c r="W17" s="253"/>
+      <c r="X17" s="253"/>
+      <c r="Y17" s="253"/>
+      <c r="Z17" s="253"/>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
         <v>128</v>
       </c>
       <c r="C18" s="12">
-        <f>C5</f>
+        <f t="shared" ref="C18:L18" si="6">C5</f>
         <v>2021</v>
       </c>
       <c r="D18" s="12">
-        <f>D5</f>
+        <f t="shared" si="6"/>
         <v>2022</v>
       </c>
       <c r="E18" s="12">
-        <f>E5</f>
+        <f t="shared" si="6"/>
         <v>2023</v>
       </c>
       <c r="F18" s="12">
-        <f>F5</f>
+        <f t="shared" si="6"/>
         <v>2024</v>
       </c>
       <c r="G18" s="12">
-        <f>G5</f>
+        <f t="shared" si="6"/>
         <v>2025</v>
       </c>
       <c r="H18" s="12">
-        <f>H5</f>
+        <f t="shared" si="6"/>
         <v>2026</v>
       </c>
       <c r="I18" s="12">
-        <f>I5</f>
+        <f t="shared" si="6"/>
         <v>2027</v>
       </c>
       <c r="J18" s="12">
-        <f>J5</f>
+        <f t="shared" si="6"/>
         <v>2028</v>
       </c>
       <c r="K18" s="12">
-        <f>K5</f>
+        <f t="shared" si="6"/>
         <v>2029</v>
       </c>
       <c r="L18" s="12">
-        <f>L5</f>
+        <f t="shared" si="6"/>
         <v>2030</v>
       </c>
       <c r="O18" s="16" t="s">
         <v>128</v>
       </c>
       <c r="P18" s="12" t="str">
-        <f>P5</f>
+        <f t="shared" ref="P18:Z18" si="7">P5</f>
         <v>Q4 2024</v>
       </c>
       <c r="Q18" s="12" t="str">
-        <f>Q5</f>
+        <f t="shared" si="7"/>
         <v>Q1 2025</v>
       </c>
       <c r="R18" s="12" t="str">
-        <f>R5</f>
+        <f t="shared" si="7"/>
         <v>Q2 2025</v>
       </c>
       <c r="S18" s="12" t="str">
-        <f>S5</f>
+        <f t="shared" si="7"/>
         <v>Q3 2025</v>
       </c>
       <c r="T18" s="12" t="str">
-        <f>T5</f>
+        <f t="shared" si="7"/>
         <v>Q4 2025</v>
       </c>
       <c r="U18" s="12" t="str">
-        <f>U5</f>
+        <f t="shared" si="7"/>
         <v>Q1 2026</v>
       </c>
       <c r="V18" s="12" t="str">
-        <f>V5</f>
+        <f t="shared" si="7"/>
         <v>Q2 2026</v>
       </c>
       <c r="W18" s="12" t="str">
-        <f>W5</f>
+        <f t="shared" si="7"/>
         <v>Q3 2026</v>
       </c>
       <c r="X18" s="12" t="str">
-        <f>X5</f>
+        <f t="shared" si="7"/>
         <v>FQ1</v>
       </c>
       <c r="Y18" s="12" t="str">
-        <f>Y5</f>
+        <f t="shared" si="7"/>
         <v>FQ2</v>
       </c>
       <c r="Z18" s="12" t="str">
-        <f>Z5</f>
+        <f t="shared" si="7"/>
         <v>FQ3</v>
       </c>
     </row>
@@ -16804,23 +16807,23 @@
         <v>COGS</v>
       </c>
       <c r="C19" s="103">
-        <f>C11/C$6</f>
+        <f t="shared" ref="C19:G21" si="8">C11/C$6</f>
         <v>0.73283299846353855</v>
       </c>
       <c r="D19" s="103">
-        <f>D11/D$6</f>
+        <f t="shared" si="8"/>
         <v>0.68743681157877934</v>
       </c>
       <c r="E19" s="103">
-        <f>E11/E$6</f>
+        <f t="shared" si="8"/>
         <v>0.77761790567545963</v>
       </c>
       <c r="F19" s="103">
-        <f>F11/F$6</f>
+        <f t="shared" si="8"/>
         <v>0.71932879531423144</v>
       </c>
       <c r="G19" s="104">
-        <f>G11/G$6</f>
+        <f t="shared" si="8"/>
         <v>0.61218487394957988</v>
       </c>
       <c r="H19" s="97">
@@ -16843,35 +16846,35 @@
         <v>COGS</v>
       </c>
       <c r="P19" s="103">
-        <f>P11/P$6</f>
+        <f t="shared" ref="P19:W21" si="9">P11/P$6</f>
         <v>0.6521956087824351</v>
       </c>
       <c r="Q19" s="103">
-        <f>Q11/Q$6</f>
+        <f t="shared" si="9"/>
         <v>0.63562386980108498</v>
       </c>
       <c r="R19" s="103">
-        <f>R11/R$6</f>
+        <f t="shared" si="9"/>
         <v>0.62349522623495224</v>
       </c>
       <c r="S19" s="103">
-        <f>S11/S$6</f>
+        <f t="shared" si="9"/>
         <v>0.60244115082824756</v>
       </c>
       <c r="T19" s="103">
-        <f>T11/T$6</f>
+        <f t="shared" si="9"/>
         <v>0.59040307101727452</v>
       </c>
       <c r="U19" s="103">
-        <f>U11/U$6</f>
+        <f t="shared" si="9"/>
         <v>0.56458481192334986</v>
       </c>
       <c r="V19" s="103">
-        <f>V11/V$6</f>
+        <f t="shared" si="9"/>
         <v>0.54259197878687437</v>
       </c>
       <c r="W19" s="104">
-        <f>W11/W$6</f>
+        <f t="shared" si="9"/>
         <v>0.49775247228049146</v>
       </c>
       <c r="X19" s="97">
@@ -16886,23 +16889,23 @@
         <v>R&amp;D</v>
       </c>
       <c r="C20" s="95">
-        <f>C12/C$6</f>
+        <f t="shared" si="8"/>
         <v>0.13254934404916677</v>
       </c>
       <c r="D20" s="95">
-        <f>D12/D$6</f>
+        <f t="shared" si="8"/>
         <v>0.12360985473314531</v>
       </c>
       <c r="E20" s="95">
-        <f>E12/E$6</f>
+        <f t="shared" si="8"/>
         <v>0.15763389288569143</v>
       </c>
       <c r="F20" s="95">
-        <f>F12/F$6</f>
+        <f t="shared" si="8"/>
         <v>0.15038784233022004</v>
       </c>
       <c r="G20" s="96">
-        <f>G12/G$6</f>
+        <f t="shared" si="8"/>
         <v>0.10441176470588236</v>
       </c>
       <c r="H20" s="97">
@@ -16925,35 +16928,35 @@
         <v>R&amp;D</v>
       </c>
       <c r="P20" s="95">
-        <f>P12/P$6</f>
+        <f t="shared" si="9"/>
         <v>0.13323353293413173</v>
       </c>
       <c r="Q20" s="95">
-        <f>Q12/Q$6</f>
+        <f t="shared" si="9"/>
         <v>0.11844484629294756</v>
       </c>
       <c r="R20" s="95">
-        <f>R12/R$6</f>
+        <f t="shared" si="9"/>
         <v>9.3399750933997508E-2</v>
       </c>
       <c r="S20" s="95">
-        <f>S12/S$6</f>
+        <f t="shared" si="9"/>
         <v>0.10680034873583261</v>
       </c>
       <c r="T20" s="95">
-        <f>T12/T$6</f>
+        <f t="shared" si="9"/>
         <v>0.10057581573896353</v>
       </c>
       <c r="U20" s="95">
-        <f>U12/U$6</f>
+        <f t="shared" si="9"/>
         <v>0.10432931156848829</v>
       </c>
       <c r="V20" s="95">
-        <f>V12/V$6</f>
+        <f t="shared" si="9"/>
         <v>9.5790520384487904E-2</v>
       </c>
       <c r="W20" s="96">
-        <f>W12/W$6</f>
+        <f t="shared" si="9"/>
         <v>8.8103086604734787E-2</v>
       </c>
       <c r="X20" s="97">
@@ -16968,23 +16971,23 @@
         <v>SG&amp;A</v>
       </c>
       <c r="C21" s="95">
-        <f>C13/C$6</f>
+        <f t="shared" si="8"/>
         <v>6.5299609975180237E-2</v>
       </c>
       <c r="D21" s="95">
-        <f>D13/D$6</f>
+        <f t="shared" si="8"/>
         <v>5.9437024423987656E-2</v>
       </c>
       <c r="E21" s="95">
-        <f>E13/E$6</f>
+        <f t="shared" si="8"/>
         <v>0.12901678657074339</v>
       </c>
       <c r="F21" s="95">
-        <f>F13/F$6</f>
+        <f t="shared" si="8"/>
         <v>0.11492797213867342</v>
       </c>
       <c r="G21" s="96">
-        <f>G13/G$6</f>
+        <f t="shared" si="8"/>
         <v>5.9663865546218491E-2</v>
       </c>
       <c r="H21" s="97">
@@ -17007,35 +17010,35 @@
         <v>SG&amp;A</v>
       </c>
       <c r="P21" s="95">
-        <f>P13/P$6</f>
+        <f t="shared" si="9"/>
         <v>9.1816367265469059E-2</v>
       </c>
       <c r="Q21" s="95">
-        <f>Q13/Q$6</f>
+        <f t="shared" si="9"/>
         <v>9.2224231464737794E-2</v>
       </c>
       <c r="R21" s="95">
-        <f>R13/R$6</f>
+        <f t="shared" si="9"/>
         <v>5.4794520547945202E-2</v>
       </c>
       <c r="S21" s="95">
-        <f>S13/S$6</f>
+        <f t="shared" si="9"/>
         <v>4.7079337401918046E-2</v>
       </c>
       <c r="T21" s="95">
-        <f>T13/T$6</f>
+        <f t="shared" si="9"/>
         <v>4.7600767754318617E-2</v>
       </c>
       <c r="U21" s="95">
-        <f>U13/U$6</f>
+        <f t="shared" si="9"/>
         <v>4.8970901348474094E-2</v>
       </c>
       <c r="V21" s="95">
-        <f>V13/V$6</f>
+        <f t="shared" si="9"/>
         <v>4.2426251242956577E-2</v>
       </c>
       <c r="W21" s="96">
-        <f>W13/W$6</f>
+        <f t="shared" si="9"/>
         <v>4.4051543302367394E-2</v>
       </c>
       <c r="X21" s="97">
@@ -17046,7 +17049,7 @@
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="str">
-        <f t="shared" ref="B22" si="6">B14</f>
+        <f t="shared" ref="B22" si="10">B14</f>
         <v>OpEx</v>
       </c>
       <c r="C22" s="103">
@@ -17054,79 +17057,79 @@
         <v>0.19507150455028957</v>
       </c>
       <c r="D22" s="103">
-        <f t="shared" ref="D22:L22" si="7">D14/D$6</f>
+        <f t="shared" ref="D22:L22" si="11">D14/D$6</f>
         <v>0.18533496514659714</v>
       </c>
       <c r="E22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.30999200639488411</v>
       </c>
       <c r="F22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.34446731043216716</v>
       </c>
       <c r="G22" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.1426470588235294</v>
       </c>
       <c r="H22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.13500000000000001</v>
       </c>
       <c r="I22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.13</v>
       </c>
       <c r="J22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.15</v>
       </c>
       <c r="K22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.16999999999999998</v>
       </c>
       <c r="L22" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.21</v>
       </c>
       <c r="O22" s="16" t="str">
-        <f t="shared" ref="O22" si="8">O14</f>
+        <f t="shared" ref="O22" si="12">O14</f>
         <v>OpEx</v>
       </c>
       <c r="P22" s="103">
-        <f t="shared" ref="P22:V22" si="9">P14/P$6</f>
+        <f t="shared" ref="P22:V22" si="13">P14/P$6</f>
         <v>0.39321357285429143</v>
       </c>
       <c r="Q22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.21338155515370705</v>
       </c>
       <c r="R22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.14404317144043172</v>
       </c>
       <c r="S22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>6.6259808195292064E-2</v>
       </c>
       <c r="T22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.14856046065259118</v>
       </c>
       <c r="U22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.15436479772888573</v>
       </c>
       <c r="V22" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>0.1564468014584024</v>
       </c>
       <c r="W22" s="104">
-        <f t="shared" ref="W22:X22" si="10">W14/W$6</f>
+        <f t="shared" ref="W22:X22" si="14">W14/W$6</f>
         <v>0.14563979622415343</v>
       </c>
       <c r="X22" s="103">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>0.12</v>
       </c>
       <c r="Y22" s="16"/>
@@ -17182,60 +17185,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
-      <c r="S3" s="254"/>
-      <c r="T3" s="254"/>
-      <c r="U3" s="254"/>
-      <c r="V3" s="254"/>
-      <c r="W3" s="254"/>
-      <c r="X3" s="254"/>
-      <c r="Y3" s="254"/>
-      <c r="Z3" s="254"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="254"/>
-      <c r="Q5" s="254"/>
-      <c r="R5" s="254"/>
-      <c r="S5" s="254"/>
-      <c r="T5" s="254"/>
-      <c r="U5" s="254"/>
-      <c r="V5" s="254"/>
-      <c r="W5" s="254"/>
-      <c r="X5" s="254"/>
-      <c r="Y5" s="254"/>
-      <c r="Z5" s="254"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17421,30 +17424,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="251" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="254"/>
-      <c r="Q11" s="254"/>
-      <c r="R11" s="254"/>
-      <c r="S11" s="254"/>
-      <c r="T11" s="254"/>
-      <c r="U11" s="254"/>
-      <c r="V11" s="254"/>
-      <c r="W11" s="254"/>
-      <c r="X11" s="254"/>
-      <c r="Y11" s="254"/>
-      <c r="Z11" s="254"/>
+      <c r="P11" s="256"/>
+      <c r="Q11" s="256"/>
+      <c r="R11" s="256"/>
+      <c r="S11" s="256"/>
+      <c r="T11" s="256"/>
+      <c r="U11" s="256"/>
+      <c r="V11" s="256"/>
+      <c r="W11" s="256"/>
+      <c r="X11" s="256"/>
+      <c r="Y11" s="256"/>
+      <c r="Z11" s="256"/>
       <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17686,18 +17689,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="251" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17910,23 +17913,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="254"/>
-      <c r="C25" s="254"/>
+      <c r="B25" s="256"/>
+      <c r="C25" s="256"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="109"/>
-      <c r="C26" s="240" t="s">
+      <c r="C26" s="251" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="240"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18118,18 +18121,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="109"/>
-      <c r="C33" s="240" t="s">
+      <c r="C33" s="251" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="E33" s="240"/>
-      <c r="F33" s="240"/>
-      <c r="G33" s="240"/>
-      <c r="H33" s="240"/>
-      <c r="I33" s="240"/>
-      <c r="J33" s="240"/>
-      <c r="K33" s="240"/>
-      <c r="L33" s="240"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
+      <c r="I33" s="251"/>
+      <c r="J33" s="251"/>
+      <c r="K33" s="251"/>
+      <c r="L33" s="251"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18313,18 +18316,18 @@
       <c r="C39" s="125"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="240" t="s">
+      <c r="C40" s="251" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="240"/>
-      <c r="E40" s="240"/>
-      <c r="F40" s="240"/>
-      <c r="G40" s="240"/>
-      <c r="H40" s="240"/>
-      <c r="I40" s="240"/>
-      <c r="J40" s="240"/>
-      <c r="K40" s="240"/>
-      <c r="L40" s="240"/>
+      <c r="D40" s="251"/>
+      <c r="E40" s="251"/>
+      <c r="F40" s="251"/>
+      <c r="G40" s="251"/>
+      <c r="H40" s="251"/>
+      <c r="I40" s="251"/>
+      <c r="J40" s="251"/>
+      <c r="K40" s="251"/>
+      <c r="L40" s="251"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18588,12 +18591,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18601,6 +18598,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18638,60 +18641,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="254"/>
-      <c r="U2" s="254"/>
-      <c r="V2" s="254"/>
-      <c r="W2" s="254"/>
-      <c r="X2" s="254"/>
-      <c r="Y2" s="254"/>
-      <c r="Z2" s="254"/>
-      <c r="AA2" s="254"/>
-      <c r="AB2" s="254"/>
-      <c r="AC2" s="254"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256"/>
+      <c r="AB2" s="256"/>
+      <c r="AC2" s="256"/>
       <c r="AE2" s="109"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="S4" s="254"/>
-      <c r="T4" s="254"/>
-      <c r="U4" s="254"/>
-      <c r="V4" s="254"/>
-      <c r="W4" s="254"/>
-      <c r="X4" s="254"/>
-      <c r="Y4" s="254"/>
-      <c r="Z4" s="254"/>
-      <c r="AA4" s="254"/>
-      <c r="AB4" s="254"/>
-      <c r="AC4" s="254"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="S4" s="256"/>
+      <c r="T4" s="256"/>
+      <c r="U4" s="256"/>
+      <c r="V4" s="256"/>
+      <c r="W4" s="256"/>
+      <c r="X4" s="256"/>
+      <c r="Y4" s="256"/>
+      <c r="Z4" s="256"/>
+      <c r="AA4" s="256"/>
+      <c r="AB4" s="256"/>
+      <c r="AC4" s="256"/>
       <c r="AE4" s="110"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19054,18 +19057,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="240" t="s">
+      <c r="C13" s="251" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="E13" s="240"/>
-      <c r="F13" s="240"/>
-      <c r="G13" s="240"/>
-      <c r="H13" s="240"/>
-      <c r="I13" s="240"/>
-      <c r="J13" s="240"/>
-      <c r="K13" s="240"/>
-      <c r="L13" s="240"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="251"/>
+      <c r="K13" s="251"/>
+      <c r="L13" s="251"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19158,18 +19161,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="240" t="s">
+      <c r="C18" s="251" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="240"/>
-      <c r="E18" s="240"/>
-      <c r="F18" s="240"/>
-      <c r="G18" s="240"/>
-      <c r="H18" s="240"/>
-      <c r="I18" s="240"/>
-      <c r="J18" s="240"/>
-      <c r="K18" s="240"/>
-      <c r="L18" s="240"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19361,18 +19364,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="240" t="s">
+      <c r="C25" s="251" t="s">
         <v>266</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="E25" s="240"/>
-      <c r="F25" s="240"/>
-      <c r="G25" s="240"/>
-      <c r="H25" s="240"/>
-      <c r="I25" s="240"/>
-      <c r="J25" s="240"/>
-      <c r="K25" s="240"/>
-      <c r="L25" s="240"/>
+      <c r="D25" s="251"/>
+      <c r="E25" s="251"/>
+      <c r="F25" s="251"/>
+      <c r="G25" s="251"/>
+      <c r="H25" s="251"/>
+      <c r="I25" s="251"/>
+      <c r="J25" s="251"/>
+      <c r="K25" s="251"/>
+      <c r="L25" s="251"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19510,18 +19513,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="240" t="s">
+      <c r="C31" s="251" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="E31" s="240"/>
-      <c r="F31" s="240"/>
-      <c r="G31" s="240"/>
-      <c r="H31" s="240"/>
-      <c r="I31" s="240"/>
-      <c r="J31" s="240"/>
-      <c r="K31" s="240"/>
-      <c r="L31" s="240"/>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="251"/>
+      <c r="G31" s="251"/>
+      <c r="H31" s="251"/>
+      <c r="I31" s="251"/>
+      <c r="J31" s="251"/>
+      <c r="K31" s="251"/>
+      <c r="L31" s="251"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19660,16 +19663,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19732,10 +19735,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="242" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19752,7 +19755,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>519.79999999999995</v>
+        <v>463.51</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19761,7 +19764,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>181410.19999999998</v>
+        <v>161764.99</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19779,7 +19782,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.6789999999999998E-2</v>
+        <v>4.6039999999999998E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19820,10 +19823,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="242" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="243"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19831,7 +19834,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.6397597261507666E-3</v>
+        <v>9.6788418252569293E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19840,7 +19843,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99136024027384928</v>
+        <v>0.99032115817474309</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19858,7 +19861,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14436349999999998</v>
+        <v>0.14361350000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19867,7 +19870,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14335512340320189</v>
+        <v>0.14249110762599682</v>
       </c>
     </row>
   </sheetData>
@@ -19912,60 +19915,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
-      <c r="S3" s="254"/>
-      <c r="T3" s="254"/>
-      <c r="U3" s="254"/>
-      <c r="V3" s="254"/>
-      <c r="W3" s="254"/>
-      <c r="X3" s="254"/>
-      <c r="Y3" s="254"/>
-      <c r="Z3" s="254"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="254"/>
-      <c r="Q5" s="254"/>
-      <c r="R5" s="254"/>
-      <c r="S5" s="254"/>
-      <c r="T5" s="254"/>
-      <c r="U5" s="254"/>
-      <c r="V5" s="254"/>
-      <c r="W5" s="254"/>
-      <c r="X5" s="254"/>
-      <c r="Y5" s="254"/>
-      <c r="Z5" s="254"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20211,10 +20214,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="243" t="s">
+      <c r="B13" s="242" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="243"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20234,10 +20237,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="243" t="s">
+      <c r="B18" s="242" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="243"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20351,37 +20354,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20570,18 +20573,18 @@
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C10" s="240" t="s">
+      <c r="C10" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
+      <c r="D10" s="251"/>
+      <c r="E10" s="251"/>
+      <c r="F10" s="251"/>
+      <c r="G10" s="251"/>
+      <c r="H10" s="251"/>
+      <c r="I10" s="251"/>
+      <c r="J10" s="251"/>
+      <c r="K10" s="251"/>
+      <c r="L10" s="251"/>
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -20775,18 +20778,18 @@
       <c r="N15" s="91"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="240" t="s">
+      <c r="C16" s="251" t="s">
         <v>195</v>
       </c>
-      <c r="D16" s="240"/>
-      <c r="E16" s="240"/>
-      <c r="F16" s="240"/>
-      <c r="G16" s="240"/>
-      <c r="H16" s="240"/>
-      <c r="I16" s="240"/>
-      <c r="J16" s="240"/>
-      <c r="K16" s="240"/>
-      <c r="L16" s="240"/>
+      <c r="D16" s="251"/>
+      <c r="E16" s="251"/>
+      <c r="F16" s="251"/>
+      <c r="G16" s="251"/>
+      <c r="H16" s="251"/>
+      <c r="I16" s="251"/>
+      <c r="J16" s="251"/>
+      <c r="K16" s="251"/>
+      <c r="L16" s="251"/>
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
@@ -20920,18 +20923,18 @@
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="240" t="s">
+      <c r="C21" s="251" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="E21" s="240"/>
-      <c r="F21" s="240"/>
-      <c r="G21" s="240"/>
-      <c r="H21" s="240"/>
-      <c r="I21" s="240"/>
-      <c r="J21" s="240"/>
-      <c r="K21" s="240"/>
-      <c r="L21" s="240"/>
+      <c r="D21" s="251"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
+      <c r="I21" s="251"/>
+      <c r="J21" s="251"/>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
@@ -21015,18 +21018,18 @@
       <c r="N25" s="91"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C26" s="240" t="s">
+      <c r="C26" s="251" t="s">
         <v>199</v>
       </c>
-      <c r="D26" s="240"/>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
@@ -21296,10 +21299,10 @@
       <c r="N36" s="91"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="242" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="243"/>
+      <c r="C37" s="242"/>
       <c r="N37" s="91"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21392,10 +21395,10 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="243" t="s">
+      <c r="B49" s="242" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="243"/>
+      <c r="C49" s="242"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21451,10 +21454,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="243" t="s">
+      <c r="B57" s="242" t="s">
         <v>326</v>
       </c>
-      <c r="C57" s="243"/>
+      <c r="C57" s="242"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21594,10 +21597,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="242" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="243"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21651,7 +21654,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>519.79999999999995</v>
+        <v>463.51</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21660,7 +21663,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.82147990745621413</v>
+        <v>-0.79979990916213262</v>
       </c>
     </row>
   </sheetData>
@@ -21716,37 +21719,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="243" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21859,18 +21862,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="240" t="s">
+      <c r="C9" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21991,18 +21994,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="240" t="s">
+      <c r="C14" s="251" t="s">
         <v>375</v>
       </c>
-      <c r="D14" s="240"/>
-      <c r="E14" s="240"/>
-      <c r="F14" s="240"/>
-      <c r="G14" s="240"/>
-      <c r="H14" s="240"/>
-      <c r="I14" s="240"/>
-      <c r="J14" s="240"/>
-      <c r="K14" s="240"/>
-      <c r="L14" s="240"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="251"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="251"/>
+      <c r="J14" s="251"/>
+      <c r="K14" s="251"/>
+      <c r="L14" s="251"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22092,10 +22095,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="243" t="s">
+      <c r="B20" s="242" t="s">
         <v>377</v>
       </c>
-      <c r="C20" s="243"/>
+      <c r="C20" s="242"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22196,60 +22199,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="243" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="243"/>
-      <c r="K3" s="243"/>
-      <c r="L3" s="243"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
-      <c r="S3" s="254"/>
-      <c r="T3" s="254"/>
-      <c r="U3" s="254"/>
-      <c r="V3" s="254"/>
-      <c r="W3" s="254"/>
-      <c r="X3" s="254"/>
-      <c r="Y3" s="254"/>
-      <c r="Z3" s="254"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="109"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="240" t="s">
+      <c r="C5" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="P5" s="254"/>
-      <c r="Q5" s="254"/>
-      <c r="R5" s="254"/>
-      <c r="S5" s="254"/>
-      <c r="T5" s="254"/>
-      <c r="U5" s="254"/>
-      <c r="V5" s="254"/>
-      <c r="W5" s="254"/>
-      <c r="X5" s="254"/>
-      <c r="Y5" s="254"/>
-      <c r="Z5" s="254"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="110"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22478,10 +22481,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="257" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="256"/>
+      <c r="C14" s="258"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -22489,7 +22492,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>519.79999999999995</v>
+        <v>463.51</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22508,20 +22511,20 @@
       <c r="C17" s="158">
         <v>0.746</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="259" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="257" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="256"/>
+      <c r="C19" s="258"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -22555,7 +22558,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>179330.99999999997</v>
+        <v>159910.94999999998</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22582,15 +22585,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>178861.99999999997</v>
+        <v>159441.94999999998</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="255" t="s">
+      <c r="B28" s="257" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="256"/>
+      <c r="C28" s="258"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -22665,18 +22668,18 @@
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C39" s="240" t="s">
+      <c r="C39" s="251" t="s">
         <v>228</v>
       </c>
-      <c r="D39" s="240"/>
-      <c r="E39" s="240"/>
-      <c r="F39" s="240"/>
-      <c r="G39" s="240"/>
-      <c r="H39" s="240"/>
-      <c r="I39" s="240"/>
-      <c r="J39" s="240"/>
-      <c r="K39" s="240"/>
-      <c r="L39" s="240"/>
+      <c r="D39" s="251"/>
+      <c r="E39" s="251"/>
+      <c r="F39" s="251"/>
+      <c r="G39" s="251"/>
+      <c r="H39" s="251"/>
+      <c r="I39" s="251"/>
+      <c r="J39" s="251"/>
+      <c r="K39" s="251"/>
+      <c r="L39" s="251"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="12">
@@ -23108,17 +23111,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29576,7 +29579,7 @@
       <c r="AA114" s="68"/>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>519.79999999999995</v>
+        <v>463.51</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29623,7 +29626,7 @@
       <c r="AA115" s="68"/>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>519.79999999999995</v>
+        <v>463.51</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -30929,7 +30932,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>31.18176364727054</v>
+        <v>27.805038992201556</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30966,7 +30969,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>16.617534176785259</v>
+        <v>14.817993971299991</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -31003,7 +31006,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>18.525929752066112</v>
+        <v>16.519726239669421</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31040,7 +31043,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>181410.19999999998</v>
+        <v>161764.99</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31077,7 +31080,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>180941.19999999998</v>
+        <v>161295.99</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31114,7 +31117,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>15.363946675723867</v>
+        <v>13.695846989895559</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31151,7 +31154,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>50.683809523809522</v>
+        <v>45.180949579831932</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31286,7 +31289,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
         <f t="shared" ref="AC157:AC158" ca="1" si="95">AC151/AC155</f>
-        <v>41.295287958115182</v>
+        <v>36.823353061689048</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31323,7 +31326,7 @@
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
         <f t="shared" ca="1" si="95"/>
-        <v>62.567178930517478</v>
+        <v>55.774113729238877</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31360,7 +31363,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
         <f t="shared" ref="AC159" ca="1" si="98">AC155/AC151</f>
-        <v>2.4215837918705786E-2</v>
+        <v>2.7156679575722781E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31397,7 +31400,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.2070026933435941E-2</v>
+        <v>3.5964704105628791E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31434,7 +31437,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>8.6571758368603321E-4</v>
+        <v>9.7085284028392059E-4</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31471,7 +31474,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>2.0891879287934196E-2</v>
+        <v>2.3429049759159878E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31508,7 +31511,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.2407780819380611E-2</v>
+        <v>2.5129046773346941E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -32011,7 +32014,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>2.5853011572667911E-3</v>
+        <v>2.8992676351044812E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -33357,15 +33360,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="242" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="243"/>
-      <c r="E4" s="243" t="s">
+      <c r="C4" s="242"/>
+      <c r="E4" s="242" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="243"/>
-      <c r="G4" s="243"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33373,7 +33376,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>519.79999999999995</v>
+        <v>463.51</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33389,7 +33392,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>181410.19999999998</v>
+        <v>161764.99</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33409,7 +33412,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>180941.19999999998</v>
+        <v>161295.99</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33429,7 +33432,7 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>31.18176364727054</v>
+        <v>27.805038992201556</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
@@ -33449,7 +33452,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>16.617534176785259</v>
+        <v>14.817993971299991</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -33469,7 +33472,7 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>18.525929752066112</v>
+        <v>16.519726239669421</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33489,7 +33492,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>15.363946675723867</v>
+        <v>13.695846989895559</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33498,18 +33501,18 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>50.683809523809522</v>
+        <v>45.180949579831932</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="243" t="s">
+      <c r="B15" s="242" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="243"/>
-      <c r="E15" s="243" t="s">
+      <c r="C15" s="242"/>
+      <c r="E15" s="242" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="243"/>
+      <c r="F15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33560,14 +33563,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="243" t="s">
+      <c r="B21" s="242" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="243"/>
-      <c r="E21" s="243" t="s">
+      <c r="C21" s="242"/>
+      <c r="E21" s="242" t="s">
         <v>253</v>
       </c>
-      <c r="F21" s="243"/>
+      <c r="F21" s="242"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33636,14 +33639,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="243" t="s">
+      <c r="B29" s="242" t="s">
         <v>254</v>
       </c>
-      <c r="C29" s="243"/>
-      <c r="E29" s="243" t="s">
+      <c r="C29" s="242"/>
+      <c r="E29" s="242" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="243"/>
+      <c r="F29" s="242"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33719,14 +33722,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="243" t="s">
+      <c r="B37" s="242" t="s">
         <v>272</v>
       </c>
-      <c r="C37" s="243"/>
-      <c r="E37" s="243" t="s">
+      <c r="C37" s="242"/>
+      <c r="E37" s="242" t="s">
         <v>275</v>
       </c>
-      <c r="F37" s="243"/>
+      <c r="F37" s="242"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -33734,7 +33737,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>3.2070026933435941E-2</v>
+        <v>3.5964704105628791E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -33750,7 +33753,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>2.4215837918705786E-2</v>
+        <v>2.7156679575722781E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -33766,7 +33769,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>8.6571758368603321E-4</v>
+        <v>9.7085284028392059E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -33782,7 +33785,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.0891879287934196E-2</v>
+        <v>2.3429049759159878E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33791,18 +33794,18 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>2.2407780819380611E-2</v>
+        <v>2.5129046773346941E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="243" t="s">
+      <c r="B45" s="242" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="243"/>
-      <c r="E45" s="243" t="s">
+      <c r="C45" s="242"/>
+      <c r="E45" s="242" t="s">
         <v>289</v>
       </c>
-      <c r="F45" s="243"/>
+      <c r="F45" s="242"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -33835,18 +33838,18 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>2.5853011572667911E-3</v>
+        <v>2.8992676351044812E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="243" t="s">
+      <c r="B51" s="242" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="243"/>
-      <c r="E51" s="243" t="s">
+      <c r="C51" s="242"/>
+      <c r="E51" s="242" t="s">
         <v>307</v>
       </c>
-      <c r="F51" s="243"/>
+      <c r="F51" s="242"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34014,7 +34017,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>519.79999999999995</v>
+        <v>463.51</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34043,7 +34046,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>181410.19999999998</v>
+        <v>161764.99</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34072,7 +34075,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>180941.19999999998</v>
+        <v>161295.99</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34101,7 +34104,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>31.18176364727054</v>
+        <v>27.805038992201556</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34130,7 +34133,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>16.617534176785259</v>
+        <v>14.817993971299991</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34159,7 +34162,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>18.525929752066112</v>
+        <v>16.519726239669421</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34188,7 +34191,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>15.363946675723867</v>
+        <v>13.695846989895559</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34217,7 +34220,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>50.683809523809522</v>
+        <v>45.180949579831932</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34990,7 +34993,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>3.2070026933435941E-2</v>
+        <v>3.5964704105628791E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35019,7 +35022,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>2.4215837918705786E-2</v>
+        <v>2.7156679575722781E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35048,7 +35051,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>8.6571758368603321E-4</v>
+        <v>9.7085284028392059E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35077,7 +35080,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.0891879287934196E-2</v>
+        <v>2.3429049759159878E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35106,7 +35109,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>2.2407780819380611E-2</v>
+        <v>2.5129046773346941E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35342,7 +35345,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>2.5853011572667911E-3</v>
+        <v>2.8992676351044812E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35831,14 +35834,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="246" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="252"/>
-      <c r="F3" s="253" t="s">
+      <c r="D3" s="247"/>
+      <c r="F3" s="248" t="s">
         <v>318</v>
       </c>
-      <c r="G3" s="252"/>
+      <c r="G3" s="247"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36350,30 +36353,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/WDC.xlsx
+++ b/WDC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dumitrasadrian/MyStockData/Finance-StockLists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1312497E-BDDF-9E47-9A55-240E593AE8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A05E4B-E9D6-7748-858E-649B81F5D1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="400" windowWidth="20480" windowHeight="12860" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -148,7 +148,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
         </ext>
       </extLst>
     </bk>
@@ -158,12 +179,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -1461,15 +1491,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="168" formatCode="0.00_);\(0.00\)"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0_);\(#,##0.0\)"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="0.0_);\(0.0\)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="167" formatCode="0.00_);\(0.00\)"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.0_);\(0.0\)"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -2061,7 +2091,7 @@
   <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2099,10 +2129,10 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2113,9 +2143,9 @@
     <xf numFmtId="38" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="7" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2130,7 +2160,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2138,10 +2168,10 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2150,15 +2180,15 @@
     </xf>
     <xf numFmtId="37" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="7" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="10" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2190,16 +2220,16 @@
     <xf numFmtId="37" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="17" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="18" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="20" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="20" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="38" fontId="21" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="21" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2217,14 +2247,14 @@
     <xf numFmtId="37" fontId="19" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="21" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="38" fontId="19" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="18" fillId="12" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="7" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2245,11 +2275,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="23" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="23" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2257,9 +2287,9 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2270,7 +2300,7 @@
     <xf numFmtId="37" fontId="7" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="18" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2280,21 +2310,21 @@
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="7" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2303,13 +2333,13 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="18" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2338,9 +2368,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="10" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="10" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -2376,11 +2406,11 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="16" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="37" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2402,10 +2432,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2438,7 +2468,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -2478,7 +2508,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2972,7 +3002,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3267,7 +3297,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3616,7 +3646,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4050,7 +4080,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4541,7 +4571,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4965,7 +4995,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5016,16 +5046,16 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>70.367549038278426</c:v>
+                  <c:v>70.36754903827844</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>74.385831270234249</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>144.29632450961719</c:v>
+                  <c:v>144.29632450961722</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>121.55779851456865</c:v>
+                  <c:v>153.52749952390022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5135,7 +5165,7 @@
                   <c:v>-94.36090225563909</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>167.29323308270676</c:v>
+                  <c:v>211.29135338345861</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5327,7 +5357,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5778,7 +5808,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6229,7 +6259,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12767,7 +12797,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Public_domain</v>
     <v>Public domain</v>
@@ -12805,12 +12835,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>799.87</v>
-    <v>68.665000000000006</v>
-    <v>2.1682999999999999</v>
-    <v>-34.409999999999997</v>
-    <v>-6.9107000000000002E-2</v>
-    <v>1.59</v>
-    <v>3.4300000000000003E-3</v>
+    <v>73.14</v>
+    <v>2.2052999999999998</v>
+    <v>21.67</v>
+    <v>4.0654000000000003E-2</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -12818,36 +12846,50 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>467.26</v>
+    <v>580</v>
     <v>3</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46231.985171839842</v>
+    <v>46234.712935497657</v>
     <v>4</v>
-    <v>422.11</v>
-    <v>159763600171</v>
+    <v>530.55010000000004</v>
+    <v>191198607691</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>466.09</v>
-    <v>32.448399999999999</v>
-    <v>497.92</v>
-    <v>463.51</v>
-    <v>465.1</v>
+    <v>568</v>
+    <v>36.1492</v>
+    <v>533.04</v>
+    <v>554.71</v>
     <v>344682100</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>10484193</v>
-    <v>8802793</v>
+    <v>5541461</v>
+    <v>8406524</v>
     <v>2000</v>
   </rv>
   <rv s="4">
     <v>5</v>
   </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="5">
+  <rv s="6">
     <v>7</v>
     <v>10 Y TSY YLD NDX</v>
     <v>8</v>
@@ -12861,28 +12903,28 @@
     <v>Powered by Refinitiv</v>
     <v>47.14</v>
     <v>39.47</v>
-    <v>-0.37</v>
-    <v>-7.9719999999999999E-3</v>
+    <v>0.41</v>
+    <v>8.8710000000000004E-3</v>
     <v>US</v>
-    <v>46.35</v>
+    <v>46.86</v>
     <v>Index</v>
-    <v>7</v>
-    <v>45.88</v>
+    <v>10</v>
+    <v>46.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.3</v>
-    <v>46.41</v>
-    <v>46.04</v>
+    <v>46.69</v>
+    <v>46.22</v>
+    <v>46.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="4">
-    <v>8</v>
+    <v>11</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12916,8 +12958,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12939,7 +12979,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12949,6 +12988,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12984,7 +13028,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="46">
+    <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12995,16 +13039,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13105,19 +13146,13 @@
       <v>9</v>
       <v>10</v>
       <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
     </spb>
     <spb s="5">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="6">
       <v>Powered by Refinitiv</v>
@@ -13198,9 +13233,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13208,9 +13240,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="name" t="s"/>
@@ -13250,7 +13279,7 @@
       <x:numFmt numFmtId="0" formatCode="General"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <x:numFmt numFmtId="27" formatCode="m/d/yy\ h:mm"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="14" formatCode="0.00%"/>
@@ -13734,7 +13763,7 @@
       </c>
       <c r="F3" s="187">
         <f ca="1">Statement!AC151</f>
-        <v>161764.99</v>
+        <v>193593.79</v>
       </c>
       <c r="H3" s="185" t="str">
         <f>'AVG target price'!B5</f>
@@ -13758,7 +13787,7 @@
       </c>
       <c r="F4" s="188">
         <f ca="1">Statement!AC152</f>
-        <v>161295.99</v>
+        <v>193124.79</v>
       </c>
       <c r="H4" s="185" t="str">
         <f>'AVG target price'!B6</f>
@@ -13775,7 +13804,7 @@
       </c>
       <c r="C5" s="208" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>463.51</v>
+        <v>554.71</v>
       </c>
       <c r="E5" s="185" t="s">
         <v>247</v>
@@ -13797,16 +13826,16 @@
       <c r="B6" s="185" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="208" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>465.1</v>
+      <c r="C6" s="208" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="185" t="s">
         <v>241</v>
       </c>
       <c r="F6" s="190">
         <f ca="1">Statement!AC148</f>
-        <v>27.805038992201556</v>
+        <v>33.275944811037789</v>
       </c>
       <c r="H6" s="185" t="str">
         <f>'AVG target price'!B8</f>
@@ -13823,14 +13852,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-34.409999999999997</v>
+        <v>21.67</v>
       </c>
       <c r="E7" s="186" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="191">
         <f ca="1">Statement!AC149</f>
-        <v>14.817993971299991</v>
+        <v>17.733575188927574</v>
       </c>
       <c r="H7" s="184" t="str">
         <f>'AVG target price'!B9</f>
@@ -13845,16 +13874,16 @@
       <c r="B8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>1.59</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>269</v>
       </c>
       <c r="F8" s="192">
         <f ca="1">Statement!AC159</f>
-        <v>2.7156679575722781E-2</v>
+        <v>2.2691843576180825E-2</v>
       </c>
       <c r="H8" s="184" t="str">
         <f>'AVG target price'!B11</f>
@@ -13862,7 +13891,7 @@
       </c>
       <c r="I8" s="213">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.79979990916213262</v>
+        <v>-0.83271485261801681</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13871,30 +13900,30 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-6.9107000000000002E-2</v>
+        <v>4.0654000000000003E-2</v>
       </c>
       <c r="E9" s="185" t="s">
         <v>292</v>
       </c>
       <c r="F9" s="192">
         <f ca="1">Statement!AC160</f>
-        <v>3.5964704105628791E-2</v>
+        <v>3.005173874637198E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>3.4300000000000003E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="185" t="s">
         <v>297</v>
       </c>
       <c r="F10" s="192">
         <f ca="1">Statement!AC162</f>
-        <v>2.3429049759159878E-2</v>
+        <v>1.9577074243962059E-2</v>
       </c>
       <c r="H10" s="184" t="s">
         <v>372</v>
@@ -13917,7 +13946,7 @@
       </c>
       <c r="F11" s="193">
         <f ca="1">Statement!AC161</f>
-        <v>9.7085284028392059E-4</v>
+        <v>8.1123469921220092E-4</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -13926,7 +13955,7 @@
       </c>
       <c r="C12" s="209" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>68.665000000000006</v>
+        <v>73.14</v>
       </c>
       <c r="E12" s="185" t="s">
         <v>101</v>
@@ -13942,7 +13971,7 @@
       </c>
       <c r="C13" s="209" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.1682999999999999</v>
+        <v>2.2052999999999998</v>
       </c>
       <c r="E13" s="185" t="s">
         <v>103</v>
@@ -13958,7 +13987,7 @@
       </c>
       <c r="C14" s="210" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>8802793</v>
+        <v>8406524</v>
       </c>
       <c r="E14" s="186" t="s">
         <v>104</v>
@@ -13974,7 +14003,7 @@
       </c>
       <c r="F15" s="192">
         <f ca="1">Statement!AC174</f>
-        <v>2.8992676351044812E-3</v>
+        <v>2.4225983695034844E-3</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -14079,12 +14108,12 @@
       <c r="C26" s="170">
         <v>0.21</v>
       </c>
-      <c r="E26" s="185" t="e" vm="2">
+      <c r="E26" s="185" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="219" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>46.04</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14099,7 +14128,7 @@
       </c>
       <c r="F27" s="220">
         <f ca="1">F26/1000</f>
-        <v>4.6039999999999998E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19755,7 +19784,7 @@
       </c>
       <c r="C6" s="133">
         <f ca="1">Overview!C5</f>
-        <v>463.51</v>
+        <v>554.71</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19764,7 +19793,7 @@
       </c>
       <c r="C7" s="134">
         <f ca="1">C5*C6</f>
-        <v>161764.99</v>
+        <v>193593.79</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19782,7 +19811,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Overview!F27</f>
-        <v>4.6039999999999998E-2</v>
+        <v>4.6630000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19791,7 +19820,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C13</f>
-        <v>2.1682999999999999</v>
+        <v>2.2052999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19834,7 +19863,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.6788418252569293E-3</v>
+        <v>8.100431413298817E-3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19843,7 +19872,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.99032115817474309</v>
+        <v>0.99189956858670114</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19861,7 +19890,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14361350000000001</v>
+        <v>0.14586850000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19870,7 +19899,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14249110762599682</v>
+        <v>0.14491087914896694</v>
       </c>
     </row>
   </sheetData>
@@ -20841,19 +20870,19 @@
       </c>
       <c r="C18" s="100">
         <f>Statement!M21</f>
-        <v>309</v>
+        <v>390.267</v>
       </c>
       <c r="D18" s="100">
         <f>Statement!N21</f>
-        <v>316</v>
+        <v>399.10799999999995</v>
       </c>
       <c r="E18" s="100">
         <f>Statement!O21</f>
-        <v>318</v>
+        <v>401.63399999999996</v>
       </c>
       <c r="F18" s="100">
         <f>Statement!P21</f>
-        <v>326</v>
+        <v>411.73799999999994</v>
       </c>
       <c r="G18" s="101">
         <f>Statement!Q21</f>
@@ -20888,7 +20917,7 @@
       <c r="C19" s="137"/>
       <c r="D19" s="144">
         <f>D18/C18-1</f>
-        <v>2.265372168284796E-2</v>
+        <v>2.2653721682847738E-2</v>
       </c>
       <c r="E19" s="144">
         <f t="shared" ref="E19:G19" si="6">E18/D18-1</f>
@@ -20900,7 +20929,7 @@
       </c>
       <c r="G19" s="145">
         <f t="shared" si="6"/>
-        <v>0.10122699386503076</v>
+        <v>-0.12808630731193127</v>
       </c>
       <c r="H19" s="146">
         <v>0.08</v>
@@ -21081,19 +21110,19 @@
       </c>
       <c r="C28" s="149">
         <f>C23/(C6/C18)</f>
-        <v>0.95884588110152458</v>
+        <v>1.2110223478312256</v>
       </c>
       <c r="D28" s="149">
         <f t="shared" ref="D28:G28" si="9">D23/(D6/D18)</f>
-        <v>0.62130580535305702</v>
+        <v>0.78470923216091093</v>
       </c>
       <c r="E28" s="149">
         <f t="shared" si="9"/>
-        <v>1.9857841726618706</v>
+        <v>2.5080454100719423</v>
       </c>
       <c r="F28" s="149">
         <f t="shared" si="9"/>
-        <v>3.9102453696374861</v>
+        <v>4.9386399018521443</v>
       </c>
       <c r="G28" s="150">
         <f t="shared" si="9"/>
@@ -21112,19 +21141,19 @@
       </c>
       <c r="C29" s="143">
         <f>C23*C18</f>
-        <v>16225.59</v>
+        <v>20492.920169999998</v>
       </c>
       <c r="D29" s="143">
         <f t="shared" ref="D29:G29" si="10">D23*D18</f>
-        <v>11676.2</v>
+        <v>14747.040599999998</v>
       </c>
       <c r="E29" s="143">
         <f t="shared" si="10"/>
-        <v>12421.08</v>
+        <v>15687.82404</v>
       </c>
       <c r="F29" s="143">
         <f t="shared" si="10"/>
-        <v>24701.02</v>
+        <v>31197.388259999992</v>
       </c>
       <c r="G29" s="151">
         <f t="shared" si="10"/>
@@ -21205,19 +21234,19 @@
       </c>
       <c r="C32" s="143">
         <f>C29+C30-C31</f>
-        <v>21580.59</v>
+        <v>25847.920169999998</v>
       </c>
       <c r="D32" s="143">
         <f t="shared" ref="D32:G32" si="11">D29+D30-D31</f>
-        <v>16351.2</v>
+        <v>19422.0406</v>
       </c>
       <c r="E32" s="143">
         <f t="shared" si="11"/>
-        <v>17468.080000000002</v>
+        <v>20734.82404</v>
       </c>
       <c r="F32" s="143">
         <f t="shared" si="11"/>
-        <v>30256.02</v>
+        <v>36752.388259999992</v>
       </c>
       <c r="G32" s="151">
         <f t="shared" si="11"/>
@@ -21236,19 +21265,19 @@
       </c>
       <c r="C33" s="149">
         <f>C32/C7</f>
-        <v>17.689008196721311</v>
+        <v>21.186819811475409</v>
       </c>
       <c r="D33" s="149">
         <f t="shared" ref="D33:G33" si="12">D32/D7</f>
-        <v>6.8386449184441656</v>
+        <v>8.1229780844834796</v>
       </c>
       <c r="E33" s="149">
         <f t="shared" si="12"/>
-        <v>-31.876058394160587</v>
+        <v>-37.8372701459854</v>
       </c>
       <c r="F33" s="149">
         <f t="shared" si="12"/>
-        <v>-75.076972704714635</v>
+        <v>-91.196993200992537</v>
       </c>
       <c r="G33" s="150">
         <f t="shared" si="12"/>
@@ -21267,19 +21296,19 @@
       </c>
       <c r="C34" s="149">
         <f>C32/C8</f>
-        <v>17.25751686698867</v>
+        <v>20.670005700045813</v>
       </c>
       <c r="D34" s="149">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
-        <v>8.9613032633730558</v>
+        <v>10.644282732163019</v>
       </c>
       <c r="E34" s="149">
         <f t="shared" si="13"/>
-        <v>-38.904409799554571</v>
+        <v>-46.180008997772831</v>
       </c>
       <c r="F34" s="149">
         <f t="shared" si="13"/>
-        <v>-48.101780604133545</v>
+        <v>-58.429870047694742</v>
       </c>
       <c r="G34" s="150">
         <f t="shared" si="13"/>
@@ -21654,7 +21683,7 @@
       </c>
       <c r="C10" s="133">
         <f ca="1">Overview!C5</f>
-        <v>463.51</v>
+        <v>554.71</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21663,7 +21692,7 @@
       </c>
       <c r="C11" s="154">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.79979990916213262</v>
+        <v>-0.83271485261801681</v>
       </c>
     </row>
   </sheetData>
@@ -21802,19 +21831,19 @@
       </c>
       <c r="C6" s="230">
         <f>Statement!M25</f>
-        <v>2.66</v>
+        <v>2.1060965954077595</v>
       </c>
       <c r="D6" s="230">
         <f>Statement!N25</f>
-        <v>4.75</v>
+        <v>3.7608867775138561</v>
       </c>
       <c r="E6" s="230">
         <f>Statement!O25</f>
-        <v>-2.91</v>
+        <v>-2.3040380047505939</v>
       </c>
       <c r="F6" s="230">
         <f>Statement!P25</f>
-        <v>-2.5099999999999998</v>
+        <v>-1.9873317498020586</v>
       </c>
       <c r="G6" s="231">
         <f>Statement!Q25</f>
@@ -21929,7 +21958,7 @@
       <c r="C11" s="137"/>
       <c r="D11" s="95">
         <f>(D6-C6)/C6</f>
-        <v>0.78571428571428559</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E11" s="95">
         <f>(E6-D6)/D6</f>
@@ -21937,11 +21966,11 @@
       </c>
       <c r="F11" s="95">
         <f>(F6-E6)/E6</f>
-        <v>-0.13745704467353964</v>
+        <v>-0.13745704467353956</v>
       </c>
       <c r="G11" s="96">
         <f>(G6-F6)/F6</f>
-        <v>-2.7729083665338647</v>
+        <v>-3.2391832669322711</v>
       </c>
       <c r="H11" s="137"/>
       <c r="I11" s="137"/>
@@ -22492,7 +22521,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>463.51</v>
+        <v>554.71</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22558,7 +22587,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>159910.94999999998</v>
+        <v>191374.95</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22585,7 +22614,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>159441.94999999998</v>
+        <v>190905.95</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -24211,19 +24240,19 @@
       </c>
       <c r="M19" s="25">
         <f t="shared" si="4"/>
-        <v>305</v>
+        <v>385.21499999999997</v>
       </c>
       <c r="N19" s="25">
         <f t="shared" si="4"/>
-        <v>312</v>
+        <v>394.05599999999998</v>
       </c>
       <c r="O19" s="25">
         <f t="shared" si="4"/>
-        <v>318</v>
+        <v>401.63399999999996</v>
       </c>
       <c r="P19" s="25">
         <f t="shared" si="4"/>
-        <v>326</v>
+        <v>411.73799999999994</v>
       </c>
       <c r="Q19" s="25">
         <f t="shared" si="4"/>
@@ -24231,15 +24260,15 @@
       </c>
       <c r="T19" s="25">
         <f t="shared" ref="T19:AA19" si="5">T18*T$84</f>
-        <v>333</v>
+        <v>420.57899999999995</v>
       </c>
       <c r="U19" s="25">
         <f t="shared" si="5"/>
-        <v>344</v>
+        <v>434.47199999999998</v>
       </c>
       <c r="V19" s="25">
         <f t="shared" si="5"/>
-        <v>346</v>
+        <v>436.99799999999999</v>
       </c>
       <c r="W19" s="25">
         <f t="shared" si="5"/>
@@ -24370,19 +24399,19 @@
       </c>
       <c r="M21" s="25">
         <f t="shared" si="6"/>
-        <v>309</v>
+        <v>390.267</v>
       </c>
       <c r="N21" s="25">
         <f t="shared" si="6"/>
-        <v>316</v>
+        <v>399.10799999999995</v>
       </c>
       <c r="O21" s="25">
         <f t="shared" si="6"/>
-        <v>318</v>
+        <v>401.63399999999996</v>
       </c>
       <c r="P21" s="25">
         <f t="shared" si="6"/>
-        <v>326</v>
+        <v>411.73799999999994</v>
       </c>
       <c r="Q21" s="25">
         <f t="shared" si="6"/>
@@ -24390,15 +24419,15 @@
       </c>
       <c r="T21" s="25">
         <f t="shared" ref="T21:AA21" si="7">T20*T$84</f>
-        <v>333</v>
+        <v>420.57899999999995</v>
       </c>
       <c r="U21" s="25">
         <f t="shared" si="7"/>
-        <v>357</v>
+        <v>450.89099999999996</v>
       </c>
       <c r="V21" s="25">
         <f t="shared" si="7"/>
-        <v>357</v>
+        <v>450.89099999999996</v>
       </c>
       <c r="W21" s="25">
         <f t="shared" si="7"/>
@@ -24499,19 +24528,19 @@
       <c r="L23" s="27"/>
       <c r="M23" s="65">
         <f>M22/M$84</f>
-        <v>2.69</v>
+        <v>2.1298495645288997</v>
       </c>
       <c r="N23" s="65">
         <f>N22/N$84</f>
-        <v>4.8099999999999996</v>
+        <v>3.8083927157561361</v>
       </c>
       <c r="O23" s="65">
         <f>O22/O$84</f>
-        <v>-2.91</v>
+        <v>-2.3040380047505939</v>
       </c>
       <c r="P23" s="65">
         <f>P22/P$84</f>
-        <v>-2.5099999999999998</v>
+        <v>-1.9873317498020586</v>
       </c>
       <c r="Q23" s="65">
         <f>Q22/Q$84</f>
@@ -24519,15 +24548,15 @@
       </c>
       <c r="T23" s="65">
         <f t="shared" ref="T23:AA23" si="8">T22/T$84</f>
-        <v>-0.77</v>
+        <v>-0.60965954077593043</v>
       </c>
       <c r="U23" s="65">
         <f t="shared" si="8"/>
-        <v>0.43</v>
+        <v>0.34045922406967538</v>
       </c>
       <c r="V23" s="65">
         <f t="shared" si="8"/>
-        <v>1.32</v>
+        <v>1.0451306413301664</v>
       </c>
       <c r="W23" s="65">
         <f t="shared" si="8"/>
@@ -24629,19 +24658,19 @@
       <c r="L25" s="29"/>
       <c r="M25" s="66">
         <f>M24/M$84</f>
-        <v>2.66</v>
+        <v>2.1060965954077595</v>
       </c>
       <c r="N25" s="66">
         <f>N24/N$84</f>
-        <v>4.75</v>
+        <v>3.7608867775138561</v>
       </c>
       <c r="O25" s="66">
         <f>O24/O$84</f>
-        <v>-2.91</v>
+        <v>-2.3040380047505939</v>
       </c>
       <c r="P25" s="66">
         <f>P24/P$84</f>
-        <v>-2.5099999999999998</v>
+        <v>-1.9873317498020586</v>
       </c>
       <c r="Q25" s="66">
         <f>Q24/Q$84</f>
@@ -24651,15 +24680,15 @@
       <c r="S25" s="1"/>
       <c r="T25" s="66">
         <f t="shared" ref="T25:AA25" si="9">T24/T$84</f>
-        <v>-0.77</v>
+        <v>-0.60965954077593043</v>
       </c>
       <c r="U25" s="66">
         <f t="shared" si="9"/>
-        <v>0.42</v>
+        <v>0.33254156769596199</v>
       </c>
       <c r="V25" s="66">
         <f t="shared" si="9"/>
-        <v>1.27</v>
+        <v>1.0055423594615995</v>
       </c>
       <c r="W25" s="66">
         <f t="shared" si="9"/>
@@ -27347,19 +27376,19 @@
       <c r="L74" s="25"/>
       <c r="M74" s="25">
         <f t="shared" ref="M74:Q74" si="27">M73*M84</f>
-        <v>309</v>
+        <v>390.267</v>
       </c>
       <c r="N74" s="25">
         <f t="shared" si="27"/>
-        <v>314</v>
+        <v>396.58199999999999</v>
       </c>
       <c r="O74" s="25">
         <f t="shared" si="27"/>
-        <v>322</v>
+        <v>406.68599999999998</v>
       </c>
       <c r="P74" s="25">
         <f t="shared" si="27"/>
-        <v>343</v>
+        <v>433.20899999999995</v>
       </c>
       <c r="Q74" s="25">
         <f t="shared" si="27"/>
@@ -27367,15 +27396,15 @@
       </c>
       <c r="T74" s="25">
         <f t="shared" ref="T74" si="28">T73*T84</f>
-        <v>343</v>
+        <v>433.20899999999995</v>
       </c>
       <c r="U74" s="25">
         <f t="shared" ref="U74" si="29">U73*U84</f>
-        <v>346</v>
+        <v>436.99799999999999</v>
       </c>
       <c r="V74" s="25">
         <f t="shared" ref="V74" si="30">V73*V84</f>
-        <v>348</v>
+        <v>439.52399999999994</v>
       </c>
       <c r="W74" s="25">
         <f t="shared" ref="W74" si="31">W73*W84</f>
@@ -27476,11 +27505,11 @@
       <c r="L76" s="25"/>
       <c r="M76" s="25">
         <f t="shared" ref="M76:P76" si="35">M75*M84</f>
-        <v>4</v>
+        <v>5.0519999999999996</v>
       </c>
       <c r="N76" s="25">
         <f t="shared" si="35"/>
-        <v>4</v>
+        <v>5.0519999999999996</v>
       </c>
       <c r="O76" s="25">
         <f t="shared" si="35"/>
@@ -27547,19 +27576,19 @@
       <c r="L77" s="25"/>
       <c r="M77" s="25">
         <f t="shared" ref="M77:P77" si="38">M74+M76</f>
-        <v>313</v>
+        <v>395.31900000000002</v>
       </c>
       <c r="N77" s="25">
         <f t="shared" si="38"/>
-        <v>318</v>
+        <v>401.63400000000001</v>
       </c>
       <c r="O77" s="25">
         <f t="shared" si="38"/>
-        <v>322</v>
+        <v>406.68599999999998</v>
       </c>
       <c r="P77" s="25">
         <f t="shared" si="38"/>
-        <v>343</v>
+        <v>433.20899999999995</v>
       </c>
       <c r="Q77" s="25">
         <f>Q74+Q76</f>
@@ -27567,15 +27596,15 @@
       </c>
       <c r="T77" s="25">
         <f t="shared" ref="T77:Z77" si="39">T74+T76</f>
-        <v>343</v>
+        <v>433.20899999999995</v>
       </c>
       <c r="U77" s="25">
         <f t="shared" si="39"/>
-        <v>346</v>
+        <v>436.99799999999999</v>
       </c>
       <c r="V77" s="25">
         <f t="shared" si="39"/>
-        <v>348</v>
+        <v>439.52399999999994</v>
       </c>
       <c r="W77" s="25">
         <f t="shared" si="39"/>
@@ -27660,19 +27689,19 @@
       <c r="L79" s="25"/>
       <c r="M79" s="25">
         <f t="shared" ref="M79:P79" si="41">M78*M84</f>
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="N79" s="25">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="O79" s="25">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="P79" s="25">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="Q79" s="25">
         <f>Q78*Q84</f>
@@ -27978,28 +28007,28 @@
       <c r="K84" s="21"/>
       <c r="L84" s="21"/>
       <c r="M84" s="21">
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="N84" s="21">
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="O84" s="21">
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="P84" s="21">
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="Q84" s="21">
         <v>1</v>
       </c>
       <c r="T84" s="21">
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="U84" s="21">
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="V84" s="21">
-        <v>1</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="W84" s="21">
         <v>1</v>
@@ -29569,17 +29598,33 @@
       <c r="Q114" s="26">
         <v>63.83</v>
       </c>
-      <c r="T114" s="68"/>
-      <c r="U114" s="68"/>
-      <c r="V114" s="68"/>
-      <c r="W114" s="68"/>
-      <c r="X114" s="68"/>
-      <c r="Y114" s="68"/>
-      <c r="Z114" s="68"/>
-      <c r="AA114" s="68"/>
+      <c r="T114" s="26">
+        <v>75.77</v>
+      </c>
+      <c r="U114" s="26">
+        <v>69.05</v>
+      </c>
+      <c r="V114" s="26">
+        <v>61.42</v>
+      </c>
+      <c r="W114" s="26">
+        <v>55.8</v>
+      </c>
+      <c r="X114" s="26">
+        <v>63.83</v>
+      </c>
+      <c r="Y114" s="26">
+        <v>64.150000000000006</v>
+      </c>
+      <c r="Z114" s="26">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="AA114" s="26">
+        <v>71.2</v>
+      </c>
       <c r="AC114" s="63">
         <f ca="1">Overview!C5</f>
-        <v>463.51</v>
+        <v>554.71</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -29598,35 +29643,59 @@
       <c r="L115" s="26"/>
       <c r="M115" s="65">
         <f>M114/M84</f>
-        <v>52.51</v>
+        <v>41.575613618368962</v>
       </c>
       <c r="N115" s="65">
         <f>N114/N84</f>
-        <v>36.950000000000003</v>
+        <v>29.255740300870947</v>
       </c>
       <c r="O115" s="65">
         <f>O114/O84</f>
-        <v>39.06</v>
+        <v>30.926365795724468</v>
       </c>
       <c r="P115" s="65">
         <f>P114/P84</f>
-        <v>75.77</v>
+        <v>59.992082343626286</v>
       </c>
       <c r="Q115" s="65">
         <f>Q114/Q84</f>
         <v>63.83</v>
       </c>
-      <c r="T115" s="68"/>
-      <c r="U115" s="68"/>
-      <c r="V115" s="68"/>
-      <c r="W115" s="68"/>
-      <c r="X115" s="68"/>
-      <c r="Y115" s="68"/>
-      <c r="Z115" s="68"/>
-      <c r="AA115" s="68"/>
+      <c r="T115" s="65">
+        <f t="shared" ref="T115:AA115" si="69">T114/T84</f>
+        <v>59.992082343626286</v>
+      </c>
+      <c r="U115" s="65">
+        <f t="shared" si="69"/>
+        <v>54.671417260490898</v>
+      </c>
+      <c r="V115" s="65">
+        <f t="shared" si="69"/>
+        <v>48.63024544734759</v>
+      </c>
+      <c r="W115" s="65">
+        <f t="shared" si="69"/>
+        <v>55.8</v>
+      </c>
+      <c r="X115" s="65">
+        <f t="shared" si="69"/>
+        <v>63.83</v>
+      </c>
+      <c r="Y115" s="65">
+        <f t="shared" si="69"/>
+        <v>64.150000000000006</v>
+      </c>
+      <c r="Z115" s="65">
+        <f t="shared" si="69"/>
+        <v>68.900000000000006</v>
+      </c>
+      <c r="AA115" s="65">
+        <f t="shared" si="69"/>
+        <v>71.2</v>
+      </c>
       <c r="AC115" s="65">
         <f ca="1">AC114/AC84</f>
-        <v>463.51</v>
+        <v>554.71</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29740,19 +29809,19 @@
         <v>101</v>
       </c>
       <c r="M121" s="76">
-        <f t="shared" ref="M121:P121" si="69">M119*M120</f>
+        <f t="shared" ref="M121:P121" si="70">M119*M120</f>
         <v>3.1417419256084496E-2</v>
       </c>
       <c r="N121" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>5.7123272021021368E-2</v>
       </c>
       <c r="O121" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-3.7660158008923819E-2</v>
       </c>
       <c r="P121" s="76">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-3.1627253183396729E-2</v>
       </c>
       <c r="Q121" s="76">
@@ -29814,19 +29883,19 @@
         <v>103</v>
       </c>
       <c r="M123" s="76">
-        <f t="shared" ref="M123:P123" si="70">M121*M122</f>
+        <f t="shared" ref="M123:P123" si="71">M121*M122</f>
         <v>7.6578677362186376E-2</v>
       </c>
       <c r="N123" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0.12273954668194094</v>
       </c>
       <c r="O123" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>-8.4816078178298143E-2</v>
       </c>
       <c r="P123" s="76">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>-7.0715474209650589E-2</v>
       </c>
       <c r="Q123" s="76">
@@ -29988,35 +30057,35 @@
       <c r="P129" s="49"/>
       <c r="Q129" s="49"/>
       <c r="T129" s="25">
-        <f t="shared" ref="T129:AA129" si="71">U5</f>
+        <f t="shared" ref="T129:AA129" si="72">U5</f>
         <v>2212</v>
       </c>
       <c r="U129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2409</v>
       </c>
       <c r="V129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2294</v>
       </c>
       <c r="W129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2605</v>
       </c>
       <c r="X129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2818</v>
       </c>
       <c r="Y129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>3017</v>
       </c>
       <c r="Z129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>3337</v>
       </c>
       <c r="AA129" s="25">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="AC129" s="49"/>
@@ -30041,31 +30110,31 @@
       <c r="P130" s="49"/>
       <c r="Q130" s="49"/>
       <c r="T130" s="225" t="str">
-        <f t="shared" ref="T130:Z130" si="72">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
+        <f t="shared" ref="T130:Z130" si="73">IF(T129&gt;T128, "BEAT", IF(T129&lt;T127, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>MISSED</v>
       </c>
       <c r="V130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>MISSED</v>
       </c>
       <c r="W130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="X130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="Y130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="Z130" s="225" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>BEAT</v>
       </c>
       <c r="AA130" s="225" t="str">
@@ -30184,35 +30253,35 @@
       <c r="P133" s="49"/>
       <c r="Q133" s="49"/>
       <c r="T133" s="229">
-        <f t="shared" ref="T133:AA133" si="73">U24</f>
+        <f t="shared" ref="T133:AA133" si="74">U24</f>
         <v>0.42</v>
       </c>
       <c r="U133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>1.27</v>
       </c>
       <c r="V133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>2.11</v>
       </c>
       <c r="W133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0.67</v>
       </c>
       <c r="X133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>3.07</v>
       </c>
       <c r="Y133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>4.7300000000000004</v>
       </c>
       <c r="Z133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="AA133" s="229">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AC133" s="49"/>
@@ -30237,31 +30306,31 @@
       <c r="P134" s="49"/>
       <c r="Q134" s="49"/>
       <c r="T134" s="225" t="str">
-        <f t="shared" ref="T134:Z134" si="74">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
+        <f t="shared" ref="T134:Z134" si="75">IF(T133&gt;T132, "BEAT", IF(T133&lt;T131, "MISSED", "MET"))</f>
         <v>MISSED</v>
       </c>
       <c r="U134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
       <c r="V134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>BEAT</v>
       </c>
       <c r="W134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>MISSED</v>
       </c>
       <c r="X134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>BEAT</v>
       </c>
       <c r="Y134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>BEAT</v>
       </c>
       <c r="Z134" s="225" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>BEAT</v>
       </c>
       <c r="AA134" s="225" t="str">
@@ -30354,55 +30423,55 @@
         <v>138</v>
       </c>
       <c r="M139" s="118">
-        <f t="shared" ref="M139:Q140" si="75">M29/M5*365</f>
+        <f t="shared" ref="M139:Q140" si="76">M29/M5*365</f>
         <v>48.682484339912541</v>
       </c>
       <c r="N139" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>54.459639227371895</v>
       </c>
       <c r="O139" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>93.248601119104706</v>
       </c>
       <c r="P139" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>125.15276238720912</v>
       </c>
       <c r="Q139" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>56.97373949579832</v>
       </c>
       <c r="T139" s="118">
-        <f t="shared" ref="T139:AA139" si="76">T29/T5*90</f>
+        <f t="shared" ref="T139:AA139" si="77">T29/T5*90</f>
         <v>97.275449101796411</v>
       </c>
       <c r="U139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>100.00904159132007</v>
       </c>
       <c r="V139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>97.023661270236616</v>
       </c>
       <c r="W139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>57.632955536181342</v>
       </c>
       <c r="X139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>51.339731285988485</v>
       </c>
       <c r="Y139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>43.275372604684172</v>
       </c>
       <c r="Z139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>50.265164070268483</v>
       </c>
       <c r="AA139" s="118">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>51.081810008990111</v>
       </c>
       <c r="AC139" s="118">
@@ -30415,55 +30484,55 @@
         <v>139</v>
       </c>
       <c r="M140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>106.43012660269333</v>
       </c>
       <c r="N140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>102.78427122842326</v>
       </c>
       <c r="O140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>277.5020559210526</v>
       </c>
       <c r="P140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>268.44850352112672</v>
       </c>
       <c r="Q140" s="118">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>80.853637611530544</v>
       </c>
       <c r="T140" s="118">
-        <f t="shared" ref="T140:AA140" si="77">T30/T6*365</f>
+        <f t="shared" ref="T140:AA140" si="78">T30/T6*365</f>
         <v>933.3052792654936</v>
       </c>
       <c r="U140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>878.49217638691323</v>
       </c>
       <c r="V140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>831.09187749667115</v>
       </c>
       <c r="W140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>346.24819102749638</v>
       </c>
       <c r="X140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>306.38166449934982</v>
       </c>
       <c r="Y140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>319.5757385292269</v>
       </c>
       <c r="Z140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>300.7849725106903</v>
       </c>
       <c r="AA140" s="118">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>298.19686935580978</v>
       </c>
       <c r="AC140" s="118">
@@ -30496,35 +30565,35 @@
         <v>79.287920384351409</v>
       </c>
       <c r="T141" s="118">
-        <f t="shared" ref="T141:AA141" si="78">T37/T6*90</f>
+        <f t="shared" ref="T141:AA141" si="79">T37/T6*90</f>
         <v>97.161438408569239</v>
       </c>
       <c r="U141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>101.0099573257468</v>
       </c>
       <c r="V141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>97.490013315579233</v>
       </c>
       <c r="W141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>83.813314037626625</v>
       </c>
       <c r="X141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>74.083224967490253</v>
       </c>
       <c r="Y141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>86.719044626021372</v>
       </c>
       <c r="Z141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>82.30299328039095</v>
       </c>
       <c r="AA141" s="118">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>85.990367248645398</v>
       </c>
       <c r="AC141" s="118">
@@ -30541,55 +30610,55 @@
         <v>98.188975751895441</v>
       </c>
       <c r="N142" s="118">
-        <f t="shared" ref="N142:Q142" si="79">N139+N140-N141</f>
+        <f t="shared" ref="N142:Q142" si="80">N139+N140-N141</f>
         <v>103.50677909887901</v>
       </c>
       <c r="O142" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>273.72249092173627</v>
       </c>
       <c r="P142" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>280.26169724636401</v>
       </c>
       <c r="Q142" s="118">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>58.539456722977448</v>
       </c>
       <c r="T142" s="118">
-        <f t="shared" ref="T142" si="80">T139+T140-T141</f>
+        <f t="shared" ref="T142" si="81">T139+T140-T141</f>
         <v>933.41928995872081</v>
       </c>
       <c r="U142" s="118">
-        <f t="shared" ref="U142" si="81">U139+U140-U141</f>
+        <f t="shared" ref="U142" si="82">U139+U140-U141</f>
         <v>877.49126065248652</v>
       </c>
       <c r="V142" s="118">
-        <f t="shared" ref="V142" si="82">V139+V140-V141</f>
+        <f t="shared" ref="V142" si="83">V139+V140-V141</f>
         <v>830.62552545132849</v>
       </c>
       <c r="W142" s="118">
-        <f t="shared" ref="W142" si="83">W139+W140-W141</f>
+        <f t="shared" ref="W142" si="84">W139+W140-W141</f>
         <v>320.06783252605106</v>
       </c>
       <c r="X142" s="118">
-        <f t="shared" ref="X142" si="84">X139+X140-X141</f>
+        <f t="shared" ref="X142" si="85">X139+X140-X141</f>
         <v>283.63817081784805</v>
       </c>
       <c r="Y142" s="118">
-        <f t="shared" ref="Y142" si="85">Y139+Y140-Y141</f>
+        <f t="shared" ref="Y142" si="86">Y139+Y140-Y141</f>
         <v>276.1320665078897</v>
       </c>
       <c r="Z142" s="118">
-        <f t="shared" ref="Z142:AA142" si="86">Z139+Z140-Z141</f>
+        <f t="shared" ref="Z142:AA142" si="87">Z139+Z140-Z141</f>
         <v>268.74714330056781</v>
       </c>
       <c r="AA142" s="118">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>263.28831211615449</v>
       </c>
       <c r="AC142" s="118">
-        <f t="shared" ref="AC142" si="87">AC139+AC140-AC141</f>
+        <f t="shared" ref="AC142" si="88">AC139+AC140-AC141</f>
         <v>45.63792664889867</v>
       </c>
     </row>
@@ -30618,35 +30687,35 @@
         <v>0.88702692524948223</v>
       </c>
       <c r="T143" s="118">
-        <f t="shared" ref="T143:AA143" si="88">T106/T48</f>
+        <f t="shared" ref="T143:AA143" si="89">T106/T48</f>
         <v>0.68718801996672207</v>
       </c>
       <c r="U143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.63557502361934204</v>
       </c>
       <c r="V143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.60790624742097876</v>
       </c>
       <c r="W143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>1.4164574077651149</v>
       </c>
       <c r="X143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.88702692524948223</v>
       </c>
       <c r="Y143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.79534646739130432</v>
       </c>
       <c r="Z143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.65461960343130365</v>
       </c>
       <c r="AA143" s="118">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0.16332644628099174</v>
       </c>
       <c r="AC143" s="118">
@@ -30679,35 +30748,35 @@
         <v>0.48898512521182452</v>
       </c>
       <c r="T144" s="179">
-        <f t="shared" ref="T144:AA144" si="89">(T106-T105)/T48</f>
+        <f t="shared" ref="T144:AA144" si="90">(T106-T105)/T48</f>
         <v>0.51349602514327974</v>
       </c>
       <c r="U144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.48913510263677745</v>
       </c>
       <c r="V144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.41883304448295783</v>
       </c>
       <c r="W144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.74483291481553027</v>
       </c>
       <c r="X144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.48898512521182452</v>
       </c>
       <c r="Y144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.44752038043478259</v>
       </c>
       <c r="Z144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0.37688088876388692</v>
       </c>
       <c r="AA144" s="179">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-4.8450413223140497E-2</v>
       </c>
       <c r="AC144" s="179">
@@ -30740,35 +30809,35 @@
         <v>0.66445182724252494</v>
       </c>
       <c r="T145" s="118">
-        <f t="shared" ref="T145:AA145" si="90">(T105+T29)/T39</f>
+        <f t="shared" ref="T145:AA145" si="91">(T105+T29)/T39</f>
         <v>0.66453096763594544</v>
       </c>
       <c r="U145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.68346741093416519</v>
       </c>
       <c r="V145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>1.0386740331491713</v>
       </c>
       <c r="W145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.95445773832497105</v>
       </c>
       <c r="X145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.66445182724252494</v>
       </c>
       <c r="Y145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.65783877827179582</v>
       </c>
       <c r="Z145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.70670013516122798</v>
       </c>
       <c r="AA145" s="118">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0.85054992452016387</v>
       </c>
       <c r="AC145" s="118">
@@ -30801,35 +30870,35 @@
         <v>1.0808416389811739</v>
       </c>
       <c r="T146" s="118">
-        <f t="shared" ref="T146:AA146" si="91">T31/T39</f>
+        <f t="shared" ref="T146:AA146" si="92">T31/T39</f>
         <v>1.3241333990471498</v>
       </c>
       <c r="U146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.4680676407814808</v>
       </c>
       <c r="V146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.9915002124946877</v>
       </c>
       <c r="W146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.5604013894249325</v>
       </c>
       <c r="X146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.0808416389811739</v>
       </c>
       <c r="Y146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.2130291900251304</v>
       </c>
       <c r="Z146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.4541417262019696</v>
       </c>
       <c r="AA146" s="118">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1.4904032779814536</v>
       </c>
       <c r="AC146" s="118">
@@ -30862,35 +30931,35 @@
         <v>7.4807692307692308</v>
       </c>
       <c r="T147" s="181" t="str">
-        <f t="shared" ref="T147:AA147" si="92">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
+        <f t="shared" ref="T147:AA147" si="93">IF(T12&gt;=0,"N/A",IF(T11&lt;=0,"N/A",T11/-T12))</f>
         <v>N/A</v>
       </c>
       <c r="U147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3.6304347826086958</v>
       </c>
       <c r="V147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>6.666666666666667</v>
       </c>
       <c r="W147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>9.3827160493827169</v>
       </c>
       <c r="X147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2.0420420420420422</v>
       </c>
       <c r="Y147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>18.857142857142858</v>
       </c>
       <c r="Z147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>21.61904761904762</v>
       </c>
       <c r="AA147" s="181">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>45.769230769230766</v>
       </c>
       <c r="AC147" s="181">
@@ -30932,7 +31001,7 @@
       <c r="AA148" s="49"/>
       <c r="AC148" s="72">
         <f ca="1">AC115/Statement!AC25</f>
-        <v>27.805038992201556</v>
+        <v>33.275944811037789</v>
       </c>
     </row>
     <row r="149" spans="2:29" x14ac:dyDescent="0.2">
@@ -30941,7 +31010,7 @@
       </c>
       <c r="M149" s="72">
         <f>M115/(Statement!M5/Statement!M21)</f>
-        <v>0.95884588110152458</v>
+        <v>0.95884588110152469</v>
       </c>
       <c r="N149" s="72">
         <f>N115/(Statement!N5/Statement!N21)</f>
@@ -30953,7 +31022,7 @@
       </c>
       <c r="P149" s="72">
         <f>P115/(Statement!P5/Statement!P21)</f>
-        <v>3.9102453696374861</v>
+        <v>3.9102453696374857</v>
       </c>
       <c r="Q149" s="72">
         <f>Q115/(Statement!Q5/Statement!Q21)</f>
@@ -30969,7 +31038,7 @@
       <c r="AA149" s="49"/>
       <c r="AC149" s="72">
         <f ca="1">AC115/(Statement!AC5/Statement!AC21)</f>
-        <v>14.817993971299991</v>
+        <v>17.733575188927574</v>
       </c>
     </row>
     <row r="150" spans="2:29" x14ac:dyDescent="0.2">
@@ -30982,7 +31051,7 @@
       </c>
       <c r="N150" s="72">
         <f>N115/(Statement!N48/Statement!N74)</f>
-        <v>0.94937402831192208</v>
+        <v>0.9493740283119223</v>
       </c>
       <c r="O150" s="72">
         <f>O115/(Statement!O48/Statement!O74)</f>
@@ -30990,23 +31059,47 @@
       </c>
       <c r="P150" s="72">
         <f>P115/(Statement!P48/Statement!P74)</f>
-        <v>2.4023950822702904</v>
+        <v>2.40239508227029</v>
       </c>
       <c r="Q150" s="72">
         <f>Q115/(Statement!Q48/Statement!Q74)</f>
         <v>4.1463660327621916</v>
       </c>
-      <c r="T150" s="49"/>
-      <c r="U150" s="49"/>
-      <c r="V150" s="49"/>
-      <c r="W150" s="49"/>
-      <c r="X150" s="49"/>
-      <c r="Y150" s="49"/>
-      <c r="Z150" s="49"/>
-      <c r="AA150" s="49"/>
+      <c r="T150" s="72">
+        <f>T115/(Statement!T48/Statement!T74)</f>
+        <v>2.40239508227029</v>
+      </c>
+      <c r="U150" s="72">
+        <f>U115/(Statement!U48/Statement!U74)</f>
+        <v>2.0519883191617283</v>
+      </c>
+      <c r="V150" s="72">
+        <f>V115/(Statement!V48/Statement!V74)</f>
+        <v>1.7639811834612527</v>
+      </c>
+      <c r="W150" s="72">
+        <f>W115/(Statement!W48/Statement!W74)</f>
+        <v>3.7616766467065865</v>
+      </c>
+      <c r="X150" s="72">
+        <f>X115/(Statement!X48/Statement!X74)</f>
+        <v>4.1463660327621916</v>
+      </c>
+      <c r="Y150" s="72">
+        <f>Y115/(Statement!Y48/Statement!Y74)</f>
+        <v>3.7261039402173917</v>
+      </c>
+      <c r="Z150" s="72">
+        <f>Z115/(Statement!Z48/Statement!Z74)</f>
+        <v>3.284643510054845</v>
+      </c>
+      <c r="AA150" s="72">
+        <f>AA115/(Statement!AA48/Statement!AA74)</f>
+        <v>2.5376033057851242</v>
+      </c>
       <c r="AC150" s="72">
         <f ca="1">AC115/(Statement!AC48/Statement!AC74)</f>
-        <v>16.519726239669421</v>
+        <v>19.770139462809919</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31019,11 +31112,11 @@
       </c>
       <c r="N151" s="143">
         <f>Statement!N115*Statement!N77</f>
-        <v>11750.1</v>
+        <v>11750.100000000002</v>
       </c>
       <c r="O151" s="143">
         <f>Statement!O115*Statement!O77</f>
-        <v>12577.320000000002</v>
+        <v>12577.32</v>
       </c>
       <c r="P151" s="143">
         <f>Statement!P115*Statement!P77</f>
@@ -31033,17 +31126,41 @@
         <f>Statement!Q115*Statement!Q77</f>
         <v>22787.309999999998</v>
       </c>
-      <c r="T151" s="49"/>
-      <c r="U151" s="49"/>
-      <c r="V151" s="49"/>
-      <c r="W151" s="49"/>
-      <c r="X151" s="49"/>
-      <c r="Y151" s="49"/>
-      <c r="Z151" s="49"/>
-      <c r="AA151" s="49"/>
+      <c r="T151" s="143">
+        <f>Statement!T115*Statement!T77</f>
+        <v>25989.109999999997</v>
+      </c>
+      <c r="U151" s="143">
+        <f>Statement!U115*Statement!U77</f>
+        <v>23891.3</v>
+      </c>
+      <c r="V151" s="143">
+        <f>Statement!V115*Statement!V77</f>
+        <v>21374.16</v>
+      </c>
+      <c r="W151" s="143">
+        <f>Statement!W115*Statement!W77</f>
+        <v>19474.2</v>
+      </c>
+      <c r="X151" s="143">
+        <f>Statement!X115*Statement!X77</f>
+        <v>22787.309999999998</v>
+      </c>
+      <c r="Y151" s="143">
+        <f>Statement!Y115*Statement!Y77</f>
+        <v>22067.600000000002</v>
+      </c>
+      <c r="Z151" s="143">
+        <f>Statement!Z115*Statement!Z77</f>
+        <v>23632.7</v>
+      </c>
+      <c r="AA151" s="143">
+        <f>Statement!AA115*Statement!AA77</f>
+        <v>24848.799999999999</v>
+      </c>
       <c r="AC151" s="143">
         <f ca="1">Statement!AC115*Statement!AC77</f>
-        <v>161764.99</v>
+        <v>193593.79</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31056,7 +31173,7 @@
       </c>
       <c r="N152" s="143">
         <f>N151+N106-N105+N47+N44</f>
-        <v>16425.099999999999</v>
+        <v>16425.100000000002</v>
       </c>
       <c r="O152" s="143">
         <f>O151+O106-O105+O47+O44</f>
@@ -31070,17 +31187,41 @@
         <f>Q151+Q106-Q105+Q47+Q44</f>
         <v>25613.309999999998</v>
       </c>
-      <c r="T152" s="49"/>
-      <c r="U152" s="49"/>
-      <c r="V152" s="49"/>
-      <c r="W152" s="49"/>
-      <c r="X152" s="49"/>
-      <c r="Y152" s="49"/>
-      <c r="Z152" s="49"/>
-      <c r="AA152" s="49"/>
+      <c r="T152" s="143">
+        <f t="shared" ref="T152:AA152" si="94">T151+T106-T105+T47+T44</f>
+        <v>31773.11</v>
+      </c>
+      <c r="U152" s="143">
+        <f t="shared" si="94"/>
+        <v>29815.3</v>
+      </c>
+      <c r="V152" s="143">
+        <f t="shared" si="94"/>
+        <v>26678.16</v>
+      </c>
+      <c r="W152" s="143">
+        <f t="shared" si="94"/>
+        <v>23559.200000000001</v>
+      </c>
+      <c r="X152" s="143">
+        <f t="shared" si="94"/>
+        <v>25613.309999999998</v>
+      </c>
+      <c r="Y152" s="143">
+        <f t="shared" si="94"/>
+        <v>24931.600000000002</v>
+      </c>
+      <c r="Z152" s="143">
+        <f t="shared" si="94"/>
+        <v>26541.7</v>
+      </c>
+      <c r="AA152" s="143">
+        <f t="shared" si="94"/>
+        <v>24379.8</v>
+      </c>
       <c r="AC152" s="143">
         <f ca="1">AC151+AC106-AC105+AC47+AC44</f>
-        <v>161295.99</v>
+        <v>193124.79</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31093,7 +31234,7 @@
       </c>
       <c r="N153" s="183">
         <f>N152/N5</f>
-        <v>0.87400095780343734</v>
+        <v>0.87400095780343756</v>
       </c>
       <c r="O153" s="183">
         <f>O152/O5</f>
@@ -31117,7 +31258,7 @@
       <c r="AA153" s="49"/>
       <c r="AC153" s="183">
         <f ca="1">AC152/AC5</f>
-        <v>13.695846989895559</v>
+        <v>16.39847074806827</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31130,7 +31271,7 @@
       </c>
       <c r="N154" s="183">
         <f>N152/N11</f>
-        <v>6.8695524884985355</v>
+        <v>6.8695524884985373</v>
       </c>
       <c r="O154" s="183">
         <f>O152/O11</f>
@@ -31154,7 +31295,7 @@
       <c r="AA154" s="49"/>
       <c r="AC154" s="183">
         <f ca="1">AC152/AC11</f>
-        <v>45.180949579831932</v>
+        <v>54.096579831932779</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31182,35 +31323,35 @@
         <v>1014</v>
       </c>
       <c r="T155" s="64">
-        <f t="shared" ref="T155:AA155" si="93">T58-T53+T108+T64</f>
+        <f t="shared" ref="T155:AA155" si="95">T58-T53+T108+T64</f>
         <v>181</v>
       </c>
       <c r="U155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>-146</v>
       </c>
       <c r="V155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>64</v>
       </c>
       <c r="W155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>384</v>
       </c>
       <c r="X155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>630</v>
       </c>
       <c r="Y155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>546</v>
       </c>
       <c r="Z155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>1146</v>
       </c>
       <c r="AA155" s="64">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>2071</v>
       </c>
       <c r="AC155" s="64">
@@ -31264,19 +31405,19 @@
         <v>37.870115207373274</v>
       </c>
       <c r="N157" s="72">
-        <f t="shared" ref="N157:Q157" si="94">N151/N155</f>
-        <v>27.199305555555558</v>
+        <f t="shared" ref="N157:Q157" si="96">N151/N155</f>
+        <v>27.199305555555561</v>
       </c>
       <c r="O157" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>-8.1301357466063351</v>
       </c>
       <c r="P157" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>-24.15344795539033</v>
       </c>
       <c r="Q157" s="72">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>22.472692307692306</v>
       </c>
       <c r="T157" s="49"/>
@@ -31288,8 +31429,8 @@
       <c r="Z157" s="49"/>
       <c r="AA157" s="49"/>
       <c r="AC157" s="72">
-        <f t="shared" ref="AC157:AC158" ca="1" si="95">AC151/AC155</f>
-        <v>36.823353061689048</v>
+        <f t="shared" ref="AC157:AC158" ca="1" si="97">AC151/AC155</f>
+        <v>44.068697928522653</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -31301,19 +31442,19 @@
         <v>22.429968797781868</v>
       </c>
       <c r="N158" s="72">
-        <f t="shared" ref="N158:Q158" si="96">N152/N156</f>
-        <v>38.981647804001199</v>
+        <f t="shared" ref="N158:Q158" si="98">N152/N156</f>
+        <v>38.981647804001206</v>
       </c>
       <c r="O158" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>-41.203385300668153</v>
       </c>
       <c r="P158" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>-50.513688394276627</v>
       </c>
       <c r="Q158" s="72">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>19.085923994038748</v>
       </c>
       <c r="T158" s="49"/>
@@ -31325,8 +31466,8 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="72">
-        <f t="shared" ca="1" si="95"/>
-        <v>55.774113729238877</v>
+        <f t="shared" ca="1" si="97"/>
+        <v>66.78011028913599</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31338,19 +31479,19 @@
         <v>2.6406045889327028E-2</v>
       </c>
       <c r="N159" s="74">
-        <f t="shared" ref="N159:Q159" si="97">N155/N151</f>
-        <v>3.6765644547705978E-2</v>
+        <f t="shared" ref="N159:Q159" si="99">N155/N151</f>
+        <v>3.6765644547705971E-2</v>
       </c>
       <c r="O159" s="74">
-        <f t="shared" si="97"/>
-        <v>-0.12299917629510895</v>
+        <f t="shared" si="99"/>
+        <v>-0.12299917629510898</v>
       </c>
       <c r="P159" s="74">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>-4.1401956434829822E-2</v>
       </c>
       <c r="Q159" s="74">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>4.4498451111605546E-2</v>
       </c>
       <c r="T159" s="49"/>
@@ -31362,8 +31503,8 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="74">
-        <f t="shared" ref="AC159" ca="1" si="98">AC155/AC151</f>
-        <v>2.7156679575722781E-2</v>
+        <f t="shared" ref="AC159" ca="1" si="100">AC155/AC151</f>
+        <v>2.2691843576180825E-2</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31400,7 +31541,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="74">
         <f ca="1">AC25/AC115</f>
-        <v>3.5964704105628791E-2</v>
+        <v>3.005173874637198E-2</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31437,7 +31578,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="154">
         <f ca="1">AC81/AC115</f>
-        <v>9.7085284028392059E-4</v>
+        <v>8.1123469921220092E-4</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31474,7 +31615,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="154">
         <f ca="1">-AC62/AC151</f>
-        <v>2.3429049759159878E-2</v>
+        <v>1.9577074243962059E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31511,7 +31652,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="154">
         <f ca="1">-(AC62+AC63)/AC151</f>
-        <v>2.5129046773346941E-2</v>
+        <v>2.0997574354012078E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -31705,11 +31846,11 @@
       </c>
       <c r="M169" s="154">
         <f>M79/M77</f>
-        <v>3.1948881789137379E-3</v>
+        <v>3.1948881789137375E-3</v>
       </c>
       <c r="N169" s="154">
         <f>N79/N77</f>
-        <v>3.1446540880503146E-3</v>
+        <v>3.1446540880503142E-3</v>
       </c>
       <c r="O169" s="154">
         <f>O79/O77</f>
@@ -31742,54 +31883,54 @@
       </c>
       <c r="M170" s="72">
         <f>M105/M74</f>
-        <v>10.906148867313917</v>
+        <v>8.6351139091954998</v>
       </c>
       <c r="N170" s="72">
         <f>N105/N74</f>
-        <v>7.4108280254777066</v>
+        <v>5.8676389750417313</v>
       </c>
       <c r="O170" s="72">
         <f>O105/O74</f>
-        <v>6.2826086956521738</v>
+        <v>4.9743536782677547</v>
       </c>
       <c r="P170" s="72">
         <f>P105/P74</f>
-        <v>5.4781341107871722</v>
+        <v>4.3373983458330745</v>
       </c>
       <c r="Q170" s="72">
         <f>Q105/Q74</f>
         <v>6.1275362318840578</v>
       </c>
       <c r="T170" s="72">
-        <f t="shared" ref="T170:AA170" si="99">T105/T74</f>
-        <v>5.4781341107871722</v>
+        <f t="shared" ref="T170:AA170" si="101">T105/T74</f>
+        <v>4.3373983458330745</v>
       </c>
       <c r="U170" s="72">
-        <f t="shared" si="99"/>
-        <v>4.9277456647398843</v>
+        <f t="shared" si="101"/>
+        <v>3.9016196870466229</v>
       </c>
       <c r="V170" s="72">
-        <f t="shared" si="99"/>
-        <v>6.583333333333333</v>
+        <f t="shared" si="101"/>
+        <v>5.2124571126946426</v>
       </c>
       <c r="W170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>9.9627507163323781</v>
       </c>
       <c r="X170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>6.1275362318840578</v>
       </c>
       <c r="Y170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>5.9883040935672511</v>
       </c>
       <c r="Z170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>5.8259587020648969</v>
       </c>
       <c r="AA170" s="72">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>5.9420289855072461</v>
       </c>
       <c r="AC170" s="72">
@@ -31822,35 +31963,35 @@
         <v>0.15671200473092844</v>
       </c>
       <c r="T171" s="154">
-        <f t="shared" ref="T171:AA171" si="100">T53/T58</f>
+        <f t="shared" ref="T171:AA171" si="102">T53/T58</f>
         <v>0.18852459016393441</v>
       </c>
       <c r="U171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>2.4705882352941178</v>
       </c>
       <c r="V171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.36842105263157893</v>
       </c>
       <c r="W171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>0.23280423280423279</v>
       </c>
       <c r="X171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>6.0321715817694369E-2</v>
       </c>
       <c r="Y171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>7.8869047619047616E-2</v>
       </c>
       <c r="Z171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>7.4805928016937195E-2</v>
       </c>
       <c r="AA171" s="154">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>6.2598425196850396E-2</v>
       </c>
       <c r="AC171" s="154">
@@ -31883,35 +32024,35 @@
         <v>2.7836134453781514E-2</v>
       </c>
       <c r="T172" s="154">
-        <f t="shared" ref="T172:AA172" si="101">T53/T5</f>
+        <f t="shared" ref="T172:AA172" si="103">T53/T5</f>
         <v>3.4431137724550899E-2</v>
       </c>
       <c r="U172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>3.7974683544303799E-2</v>
       </c>
       <c r="V172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>6.6832710668327105E-2</v>
       </c>
       <c r="W172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>9.5902353966870094E-2</v>
       </c>
       <c r="X172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.7274472168905951E-2</v>
       </c>
       <c r="Y172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>1.8807665010645847E-2</v>
       </c>
       <c r="Z172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>3.5134239310573419E-2</v>
       </c>
       <c r="AA172" s="154">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>4.7647587653581062E-2</v>
       </c>
       <c r="AC172" s="154">
@@ -31925,54 +32066,54 @@
       </c>
       <c r="M173" s="72">
         <f>(M105-M106)/M74</f>
-        <v>-17.33009708737864</v>
+        <v>-13.72137536609552</v>
       </c>
       <c r="N173" s="72">
         <f>(N105-N106)/N74</f>
-        <v>-14.888535031847134</v>
+        <v>-11.788230429015941</v>
       </c>
       <c r="O173" s="72">
         <f>(O105-O106)/O74</f>
-        <v>-15.673913043478262</v>
+        <v>-12.410065750972496</v>
       </c>
       <c r="P173" s="72">
         <f>(P105-P106)/P74</f>
-        <v>-16.195335276967931</v>
+        <v>-12.822909958011032</v>
       </c>
       <c r="Q173" s="72">
         <f>(Q105-Q106)/Q74</f>
         <v>-7.5275362318840582</v>
       </c>
       <c r="T173" s="72">
-        <f t="shared" ref="T173:AA173" si="102">(T105-T106)/T74</f>
-        <v>-16.195335276967931</v>
+        <f t="shared" ref="T173:AA173" si="104">(T105-T106)/T74</f>
+        <v>-12.822909958011032</v>
       </c>
       <c r="U173" s="72">
-        <f t="shared" si="102"/>
-        <v>-16.459537572254334</v>
+        <f t="shared" si="104"/>
+        <v>-13.032096256733441</v>
       </c>
       <c r="V173" s="72">
-        <f t="shared" si="102"/>
-        <v>-14.583333333333334</v>
+        <f t="shared" si="104"/>
+        <v>-11.546582211665349</v>
       </c>
       <c r="W173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-11.048710601719197</v>
       </c>
       <c r="X173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-7.5275362318840582</v>
       </c>
       <c r="Y173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-7.704678362573099</v>
       </c>
       <c r="Z173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>-7.9056047197640114</v>
       </c>
       <c r="AA173" s="72">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>1.3594202898550725</v>
       </c>
       <c r="AC173" s="72">
@@ -31990,11 +32131,11 @@
       </c>
       <c r="N174" s="154">
         <f>(N105-N106)/N151</f>
-        <v>-0.39786895430677183</v>
+        <v>-0.39786895430677177</v>
       </c>
       <c r="O174" s="154">
         <f>(O105-O106)/O151</f>
-        <v>-0.40127785569580798</v>
+        <v>-0.40127785569580804</v>
       </c>
       <c r="P174" s="154">
         <f>(P105-P106)/P151</f>
@@ -32014,7 +32155,7 @@
       <c r="AA174" s="49"/>
       <c r="AC174" s="154">
         <f ca="1">(AC105-AC106)/AC151</f>
-        <v>2.8992676351044812E-3</v>
+        <v>2.4225983695034844E-3</v>
       </c>
     </row>
     <row r="175" spans="2:29" x14ac:dyDescent="0.2">
@@ -32042,35 +32183,35 @@
         <v>4.3277310924369747E-2</v>
       </c>
       <c r="T175" s="154">
-        <f t="shared" ref="T175:AA175" si="103">-T108/T5</f>
+        <f t="shared" ref="T175:AA175" si="105">-T108/T5</f>
         <v>5.7884231536926151E-2</v>
       </c>
       <c r="U175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>4.3399638336347197E-2</v>
       </c>
       <c r="V175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>8.8003320880033209E-2</v>
       </c>
       <c r="W175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>0.14864864864864866</v>
       </c>
       <c r="X175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>2.72552783109405E-2</v>
       </c>
       <c r="Y175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>2.5904897090134847E-2</v>
       </c>
       <c r="Z175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>5.4690089492873718E-2</v>
       </c>
       <c r="AA175" s="154">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>9.2897812406353017E-2</v>
       </c>
       <c r="AC175" s="154">
@@ -32103,35 +32244,35 @@
         <v>0.24364281490242459</v>
       </c>
       <c r="T176" s="154">
-        <f t="shared" ref="T176:AA176" si="104">-(T108/T58)</f>
+        <f t="shared" ref="T176:AA176" si="106">-(T108/T58)</f>
         <v>0.31693989071038253</v>
       </c>
       <c r="U176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>2.8235294117647061</v>
       </c>
       <c r="V176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.48512585812356979</v>
       </c>
       <c r="W176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.36084656084656086</v>
       </c>
       <c r="X176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>9.5174262734584444E-2</v>
       </c>
       <c r="Y176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.10863095238095238</v>
       </c>
       <c r="Z176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.11644318983768526</v>
       </c>
       <c r="AA176" s="154">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>0.12204724409448819</v>
       </c>
       <c r="AC176" s="154">
@@ -32164,35 +32305,35 @@
         <v>0.91352549889135259</v>
       </c>
       <c r="T177" s="154">
-        <f t="shared" ref="T177:AA177" si="105">-T108/T52</f>
+        <f t="shared" ref="T177:AA177" si="107">-T108/T52</f>
         <v>0.84057971014492749</v>
       </c>
       <c r="U177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.71111111111111114</v>
       </c>
       <c r="V177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.83137254901960789</v>
       </c>
       <c r="W177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.9342465753424658</v>
       </c>
       <c r="X177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.82558139534883723</v>
       </c>
       <c r="Y177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.82954545454545459</v>
       </c>
       <c r="Z177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="AA177" s="154">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>1.1231884057971016</v>
       </c>
       <c r="AC177" s="154">
@@ -32474,7 +32615,7 @@
         <v>179</v>
       </c>
       <c r="AC186" s="62">
-        <f t="shared" ref="AC186:AC187" si="106">SUM(X186:AA186)</f>
+        <f t="shared" ref="AC186:AC187" si="108">SUM(X186:AA186)</f>
         <v>641</v>
       </c>
     </row>
@@ -32532,7 +32673,7 @@
         <v>186</v>
       </c>
       <c r="AC187" s="62">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>652</v>
       </c>
     </row>
@@ -32598,61 +32739,61 @@
       <c r="K191" s="81"/>
       <c r="L191" s="81"/>
       <c r="M191" s="81">
-        <f t="shared" ref="M191:Q193" si="107">IF(L185=0,
+        <f t="shared" ref="M191:Q193" si="109">IF(L185=0,
 IF(M185=0,0,IF(M185&gt;0,1,-1)),
 (M185-L185)/ABS(L185)
 )</f>
         <v>1</v>
       </c>
       <c r="N191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.4008387209505504</v>
       </c>
       <c r="O191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.40713483846825493</v>
       </c>
       <c r="P191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>6.2907637281716805E-2</v>
       </c>
       <c r="Q191" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>0.65102929532858278</v>
       </c>
       <c r="T191" s="81">
-        <f t="shared" ref="T191:AA193" si="108">IF(S185=0,
+        <f t="shared" ref="T191:AA193" si="110">IF(S185=0,
 IF(T185=0,0,IF(T185&gt;0,1,-1)),
 (T185-S185)/ABS(S185)
 )</f>
         <v>1</v>
       </c>
       <c r="U191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.11507009345794393</v>
       </c>
       <c r="V191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>9.7957045573598744E-2</v>
       </c>
       <c r="W191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>-4.2461832061068704E-2</v>
       </c>
       <c r="X191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.16043846537120079</v>
       </c>
       <c r="Y191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>7.7715757835981114E-2</v>
       </c>
       <c r="Z191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>6.4940239043824705E-2</v>
       </c>
       <c r="AA191" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.11185933408155631</v>
       </c>
       <c r="AC191" s="49"/>
@@ -32663,55 +32804,55 @@
         <v>Client</v>
       </c>
       <c r="M192" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>1</v>
       </c>
       <c r="N192" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-2.8155473149292679E-2</v>
       </c>
       <c r="O192" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.90234595816845675</v>
       </c>
       <c r="P192" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.16497829232995659</v>
       </c>
       <c r="Q192" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-3.6395147313691506E-2</v>
       </c>
       <c r="T192" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1</v>
       </c>
       <c r="U192" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.4598540145985401E-2</v>
       </c>
       <c r="V192" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>7.1942446043165471E-3</v>
       </c>
       <c r="W192" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>-2.1428571428571429E-2</v>
       </c>
       <c r="X192" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>2.1897810218978103E-2</v>
       </c>
       <c r="Y192" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>4.2857142857142858E-2</v>
       </c>
       <c r="Z192" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.20547945205479451</v>
       </c>
       <c r="AA192" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1.7045454545454544E-2</v>
       </c>
       <c r="AC192" s="49"/>
@@ -32722,55 +32863,55 @@
         <v>Consumer</v>
       </c>
       <c r="M193" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>1</v>
       </c>
       <c r="N193" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-5.5640632976008166E-2</v>
       </c>
       <c r="O193" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.78081081081081083</v>
       </c>
       <c r="P193" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-0.15166461159062886</v>
       </c>
       <c r="Q193" s="81">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>-9.4476744186046513E-2</v>
       </c>
       <c r="T193" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>1</v>
       </c>
       <c r="U193" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>5.8064516129032261E-2</v>
       </c>
       <c r="V193" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>5.4878048780487805E-2</v>
       </c>
       <c r="W193" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>-0.13294797687861271</v>
       </c>
       <c r="X193" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>-9.3333333333333338E-2</v>
       </c>
       <c r="Y193" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.19117647058823528</v>
       </c>
       <c r="Z193" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>3.7037037037037035E-2</v>
       </c>
       <c r="AA193" s="81">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>0.10714285714285714</v>
       </c>
       <c r="AC193" s="49"/>
@@ -32907,19 +33048,19 @@
       </c>
       <c r="N201" s="143">
         <f>100*(1+((N115-$M115)/ABS($M115)))</f>
-        <v>70.367549038278426</v>
+        <v>70.36754903827844</v>
       </c>
       <c r="O201" s="143">
-        <f t="shared" ref="O201:Q201" si="109">100*(1+((O115-$M115)/ABS($M115)))</f>
+        <f t="shared" ref="O201:Q201" si="111">100*(1+((O115-$M115)/ABS($M115)))</f>
         <v>74.385831270234249</v>
       </c>
       <c r="P201" s="143">
-        <f t="shared" si="109"/>
-        <v>144.29632450961719</v>
+        <f t="shared" si="111"/>
+        <v>144.29632450961722</v>
       </c>
       <c r="Q201" s="143">
-        <f t="shared" si="109"/>
-        <v>121.55779851456865</v>
+        <f t="shared" si="111"/>
+        <v>153.52749952390022</v>
       </c>
       <c r="T201" s="49"/>
       <c r="U201" s="49"/>
@@ -32976,16 +33117,16 @@
         <v>178.57142857142856</v>
       </c>
       <c r="O203" s="143">
-        <f t="shared" ref="O203:Q203" si="110">100*(1+((O25-$M25)/ABS($M25)))</f>
+        <f t="shared" ref="O203:Q203" si="112">100*(1+((O25-$M25)/ABS($M25)))</f>
         <v>-109.39849624060152</v>
       </c>
       <c r="P203" s="143">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>-94.36090225563909</v>
       </c>
       <c r="Q203" s="143">
-        <f t="shared" si="110"/>
-        <v>167.29323308270676</v>
+        <f t="shared" si="112"/>
+        <v>211.29135338345861</v>
       </c>
       <c r="T203" s="49"/>
       <c r="U203" s="49"/>
@@ -33123,7 +33264,7 @@
         <v>199</v>
       </c>
       <c r="AC208" s="62">
-        <f t="shared" ref="AC208:AC209" si="111">SUM(X208:AA208)</f>
+        <f t="shared" ref="AC208:AC209" si="113">SUM(X208:AA208)</f>
         <v>744</v>
       </c>
     </row>
@@ -33181,7 +33322,7 @@
         <v>23</v>
       </c>
       <c r="AC209" s="62">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>87</v>
       </c>
     </row>
@@ -33243,39 +33384,39 @@
         <v>13.673770491803278</v>
       </c>
       <c r="T211" s="63">
-        <f t="shared" ref="T211:AC211" si="112">T185/T208</f>
+        <f t="shared" ref="T211:AC211" si="114">T185/T208</f>
         <v>13.696</v>
       </c>
       <c r="U211" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>13.539007092198581</v>
       </c>
       <c r="V211" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>13.61038961038961</v>
       </c>
       <c r="W211" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>13.841379310344827</v>
       </c>
       <c r="X211" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>13.7</v>
       </c>
       <c r="Y211" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>13.71584699453552</v>
       </c>
       <c r="Z211" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>13.921875</v>
       </c>
       <c r="AA211" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>14.93467336683417</v>
       </c>
       <c r="AC211" s="63">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>14.091397849462366</v>
       </c>
     </row>
@@ -33376,7 +33517,7 @@
       </c>
       <c r="C5" s="172">
         <f ca="1">Overview!C5</f>
-        <v>463.51</v>
+        <v>554.71</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="132" t="s">
@@ -33392,7 +33533,7 @@
       </c>
       <c r="C6" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>161764.99</v>
+        <v>193593.79</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33412,7 +33553,7 @@
       </c>
       <c r="C7" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>161295.99</v>
+        <v>193124.79</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>30</v>
@@ -33432,14 +33573,14 @@
       </c>
       <c r="C8" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>27.805038992201556</v>
+        <v>33.275944811037789</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>247</v>
       </c>
       <c r="F8" s="178">
         <f>IF(OR(Statement!M25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(4, Statement!M25, Statement!Q25))</f>
-        <v>0.13728573964150814</v>
+        <v>0.20564772565511968</v>
       </c>
       <c r="G8" s="178" t="str">
         <f>IF(OR(Statement!H25&lt;=0, Statement!Q25&lt;=0), "N/A", _xlfn.RRI(9, Statement!H25, Statement!Q25))</f>
@@ -33452,7 +33593,7 @@
       </c>
       <c r="C9" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>14.817993971299991</v>
+        <v>17.733575188927574</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>248</v>
@@ -33472,14 +33613,14 @@
       </c>
       <c r="C10" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>16.519726239669421</v>
+        <v>19.770139462809919</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
       </c>
       <c r="F10" s="178">
         <f>IF(Statement!M115&lt;=0,"N/A",_xlfn.RRI(4,Statement!M115,Statement!Q115))</f>
-        <v>5.0015491536152146E-2</v>
+        <v>0.11313168287175834</v>
       </c>
       <c r="G10" s="178" t="str">
         <f>IF(Statement!H115&lt;=0,"N/A",_xlfn.RRI(9,Statement!H115,Statement!Q115))</f>
@@ -33492,7 +33633,7 @@
       </c>
       <c r="C11" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>13.695846989895559</v>
+        <v>16.39847074806827</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33501,7 +33642,7 @@
       </c>
       <c r="C12" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>45.180949579831932</v>
+        <v>54.096579831932779</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -33737,7 +33878,7 @@
       </c>
       <c r="C38" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>3.5964704105628791E-2</v>
+        <v>3.005173874637198E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>274</v>
@@ -33753,7 +33894,7 @@
       </c>
       <c r="C39" s="215">
         <f ca="1">Statement!AC159</f>
-        <v>2.7156679575722781E-2</v>
+        <v>2.2691843576180825E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>276</v>
@@ -33769,7 +33910,7 @@
       </c>
       <c r="C40" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>9.7085284028392059E-4</v>
+        <v>8.1123469921220092E-4</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>277</v>
@@ -33785,7 +33926,7 @@
       </c>
       <c r="C41" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.3429049759159878E-2</v>
+        <v>1.9577074243962059E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -33794,7 +33935,7 @@
       </c>
       <c r="C42" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>2.5129046773346941E-2</v>
+        <v>2.0997574354012078E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -33838,7 +33979,7 @@
       </c>
       <c r="F48" s="175">
         <f ca="1">Statement!AC174</f>
-        <v>2.8992676351044812E-3</v>
+        <v>2.4225983695034844E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34017,7 +34158,7 @@
       </c>
       <c r="I6" s="172">
         <f ca="1">Statement!AC114</f>
-        <v>463.51</v>
+        <v>554.71</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34030,11 +34171,11 @@
       </c>
       <c r="D7" s="173">
         <f>Statement!N151</f>
-        <v>11750.1</v>
+        <v>11750.100000000002</v>
       </c>
       <c r="E7" s="173">
         <f>Statement!O151</f>
-        <v>12577.320000000002</v>
+        <v>12577.32</v>
       </c>
       <c r="F7" s="173">
         <f>Statement!P151</f>
@@ -34046,7 +34187,7 @@
       </c>
       <c r="I7" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>161764.99</v>
+        <v>193593.79</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34059,7 +34200,7 @@
       </c>
       <c r="D8" s="173">
         <f>Statement!N152</f>
-        <v>16425.099999999999</v>
+        <v>16425.100000000002</v>
       </c>
       <c r="E8" s="173">
         <f>Statement!O152</f>
@@ -34075,7 +34216,7 @@
       </c>
       <c r="I8" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>161295.99</v>
+        <v>193124.79</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34104,7 +34245,7 @@
       </c>
       <c r="I9" s="174">
         <f ca="1">Statement!AC148</f>
-        <v>27.805038992201556</v>
+        <v>33.275944811037789</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34113,7 +34254,7 @@
       </c>
       <c r="C10" s="174">
         <f>Statement!M149</f>
-        <v>0.95884588110152458</v>
+        <v>0.95884588110152469</v>
       </c>
       <c r="D10" s="174">
         <f>Statement!N149</f>
@@ -34125,7 +34266,7 @@
       </c>
       <c r="F10" s="174">
         <f>Statement!P149</f>
-        <v>3.9102453696374861</v>
+        <v>3.9102453696374857</v>
       </c>
       <c r="G10" s="174">
         <f>Statement!Q149</f>
@@ -34133,7 +34274,7 @@
       </c>
       <c r="I10" s="174">
         <f ca="1">Statement!AC149</f>
-        <v>14.817993971299991</v>
+        <v>17.733575188927574</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34146,7 +34287,7 @@
       </c>
       <c r="D11" s="174">
         <f>Statement!N150</f>
-        <v>0.94937402831192208</v>
+        <v>0.9493740283119223</v>
       </c>
       <c r="E11" s="174">
         <f>Statement!O150</f>
@@ -34154,7 +34295,7 @@
       </c>
       <c r="F11" s="174">
         <f>Statement!P150</f>
-        <v>2.4023950822702904</v>
+        <v>2.40239508227029</v>
       </c>
       <c r="G11" s="174">
         <f>Statement!Q150</f>
@@ -34162,7 +34303,7 @@
       </c>
       <c r="I11" s="174">
         <f ca="1">Statement!AC150</f>
-        <v>16.519726239669421</v>
+        <v>19.770139462809919</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34175,7 +34316,7 @@
       </c>
       <c r="D12" s="174">
         <f>Statement!N153</f>
-        <v>0.87400095780343734</v>
+        <v>0.87400095780343756</v>
       </c>
       <c r="E12" s="174">
         <f>Statement!O153</f>
@@ -34191,7 +34332,7 @@
       </c>
       <c r="I12" s="174">
         <f ca="1">Statement!AC153</f>
-        <v>13.695846989895559</v>
+        <v>16.39847074806827</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34204,7 +34345,7 @@
       </c>
       <c r="D13" s="174">
         <f>Statement!N154</f>
-        <v>6.8695524884985355</v>
+        <v>6.8695524884985373</v>
       </c>
       <c r="E13" s="174">
         <f>Statement!O154</f>
@@ -34220,7 +34361,7 @@
       </c>
       <c r="I13" s="174">
         <f ca="1">Statement!AC154</f>
-        <v>45.180949579831932</v>
+        <v>54.096579831932779</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -34993,7 +35134,7 @@
       </c>
       <c r="I51" s="175">
         <f ca="1">Statement!AC160</f>
-        <v>3.5964704105628791E-2</v>
+        <v>3.005173874637198E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35006,11 +35147,11 @@
       </c>
       <c r="D52" s="175">
         <f>Statement!N159</f>
-        <v>3.6765644547705978E-2</v>
+        <v>3.6765644547705971E-2</v>
       </c>
       <c r="E52" s="175">
         <f>Statement!O159</f>
-        <v>-0.12299917629510895</v>
+        <v>-0.12299917629510898</v>
       </c>
       <c r="F52" s="175">
         <f>Statement!P159</f>
@@ -35022,7 +35163,7 @@
       </c>
       <c r="I52" s="175">
         <f ca="1">Statement!AC159</f>
-        <v>2.7156679575722781E-2</v>
+        <v>2.2691843576180825E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35051,7 +35192,7 @@
       </c>
       <c r="I53" s="175">
         <f ca="1">Statement!AC161</f>
-        <v>9.7085284028392059E-4</v>
+        <v>8.1123469921220092E-4</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
@@ -35080,7 +35221,7 @@
       </c>
       <c r="I54" s="175">
         <f ca="1">Statement!AC162</f>
-        <v>2.3429049759159878E-2</v>
+        <v>1.9577074243962059E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -35109,7 +35250,7 @@
       </c>
       <c r="I55" s="175">
         <f ca="1">Statement!AC163</f>
-        <v>2.5129046773346941E-2</v>
+        <v>2.0997574354012078E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35227,11 +35368,11 @@
       </c>
       <c r="C63" s="175">
         <f>Statement!M169</f>
-        <v>3.1948881789137379E-3</v>
+        <v>3.1948881789137375E-3</v>
       </c>
       <c r="D63" s="175">
         <f>Statement!N169</f>
-        <v>3.1446540880503146E-3</v>
+        <v>3.1446540880503142E-3</v>
       </c>
       <c r="E63" s="175">
         <f>Statement!O169</f>
@@ -35267,19 +35408,19 @@
       </c>
       <c r="C66" s="174">
         <f>Statement!M170</f>
-        <v>10.906148867313917</v>
+        <v>8.6351139091954998</v>
       </c>
       <c r="D66" s="174">
         <f>Statement!N170</f>
-        <v>7.4108280254777066</v>
+        <v>5.8676389750417313</v>
       </c>
       <c r="E66" s="174">
         <f>Statement!O170</f>
-        <v>6.2826086956521738</v>
+        <v>4.9743536782677547</v>
       </c>
       <c r="F66" s="174">
         <f>Statement!P170</f>
-        <v>5.4781341107871722</v>
+        <v>4.3373983458330745</v>
       </c>
       <c r="G66" s="174">
         <f>Statement!Q170</f>
@@ -35296,19 +35437,19 @@
       </c>
       <c r="C67" s="174">
         <f>Statement!M173</f>
-        <v>-17.33009708737864</v>
+        <v>-13.72137536609552</v>
       </c>
       <c r="D67" s="174">
         <f>Statement!N173</f>
-        <v>-14.888535031847134</v>
+        <v>-11.788230429015941</v>
       </c>
       <c r="E67" s="174">
         <f>Statement!O173</f>
-        <v>-15.673913043478262</v>
+        <v>-12.410065750972496</v>
       </c>
       <c r="F67" s="174">
         <f>Statement!P173</f>
-        <v>-16.195335276967931</v>
+        <v>-12.822909958011032</v>
       </c>
       <c r="G67" s="174">
         <f>Statement!Q173</f>
@@ -35329,11 +35470,11 @@
       </c>
       <c r="D68" s="196">
         <f>Statement!N174</f>
-        <v>-0.39786895430677183</v>
+        <v>-0.39786895430677177</v>
       </c>
       <c r="E68" s="196">
         <f>Statement!O174</f>
-        <v>-0.40127785569580798</v>
+        <v>-0.40127785569580804</v>
       </c>
       <c r="F68" s="196">
         <f>Statement!P174</f>
@@ -35345,7 +35486,7 @@
       </c>
       <c r="I68" s="196">
         <f ca="1">Statement!AC174</f>
-        <v>2.8992676351044812E-3</v>
+        <v>2.4225983695034844E-3</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -37144,7 +37285,7 @@
       </c>
       <c r="I71" s="227">
         <f>Statement!N201</f>
-        <v>70.367549038278426</v>
+        <v>70.36754903827844</v>
       </c>
       <c r="J71" s="227">
         <f>Statement!O201</f>
@@ -37152,11 +37293,11 @@
       </c>
       <c r="K71" s="227">
         <f>Statement!P201</f>
-        <v>144.29632450961719</v>
+        <v>144.29632450961722</v>
       </c>
       <c r="L71" s="227">
         <f>Statement!Q201</f>
-        <v>121.55779851456865</v>
+        <v>153.52749952390022</v>
       </c>
     </row>
     <row r="72" spans="2:12" x14ac:dyDescent="0.2">
@@ -37246,7 +37387,7 @@
       </c>
       <c r="L73" s="227">
         <f>Statement!Q203</f>
-        <v>167.29323308270676</v>
+        <v>211.29135338345861</v>
       </c>
     </row>
   </sheetData>
